--- a/test!.xlsx
+++ b/test!.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:T49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -533,7 +533,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>b389968d-2a98-4fc4-897d-8f42b672a09a</t>
+          <t>e9473717-a12e-43b3-ab10-4dc44edf94e0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -543,22 +543,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>89fcc152-069c-493d-9aeb-a97b0e1b2caf</t>
+          <t>ad7ebbd3-8ce4-4fd2-a761-b7f7468bae37</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2024-07-24T16:27:15.491305+09:00</t>
+          <t>2024-07-24T17:09:35.450759+09:00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>성매매 기소유예 선처를 받기 위하여</t>
+          <t>피해자 진술의 모순을 짚어 준강제추행죄 무죄 판결을 받은 사례</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성매매 기소유예 선처를 받기 위하여. </t>
+          <t xml:space="preserve">피해자 진술의 모순을 짚어 준강제추행죄 무죄 판결을 받은 사례. </t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>b389968d-2a98-4fc4-897d-8f42b672a09a</t>
+          <t>e9473717-a12e-43b3-ab10-4dc44edf94e0</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -633,22 +633,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0d7d8ad2-69f5-4633-a398-b23deb9b9868</t>
+          <t>bf7b8586-9257-4eca-8d05-5982dad29c87</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>b389968d-2a98-4fc4-897d-8f42b672a09a</t>
+          <t>e9473717-a12e-43b3-ab10-4dc44edf94e0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ec7a73df-84ef-41fb-b87f-bb6f8e025425</t>
+          <t>2a29b526-0bbb-4203-9a07-26a28b88ad55</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2024-07-24T16:27:15.491305+09:00</t>
+          <t>2024-07-24T17:09:35.450759+09:00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -658,49 +658,19 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>요즘은 온라인을 통해 각 나이별로 관심을 끌 수 있는
-            것들을
-            알리고 있습니다. 여기서 여성의 경우는 화장품을 세일한다는 소식에 눈길이 가게 되고 남성의 경우 컴퓨터 게임에 관련해 이벤트를 한다고 하면 관심을 갖게 되며,
-            중장년
-            층은 영양제에 관련해서 관심을 가지기 때문에 이렇게 각 연령별로 주목을 받을 수 있는 것으로 적극적으로 홍보를 하고 있습니다. 그래서 요즘은 인터넷에도 또
-            많은
-            사람들이 활동하고 있는 SNS에도 영상을 시청할 수 있는 앱에서도 광고들을 많이 접할 수 있는데, 여기서 간혹 나쁜 생각을 가지고 불순한 광고를 하여
-            형사처벌을 받게
-            되는 경우가 있습니다. 이에 관련하여서는 성범죄와 연관되어 있어서 사안이 상당히 심각하다고 보고 있다고 합니다. 성범죄는 상대방의 신체적으로 피해를 주는 것은
-            물론
-            정신적으로도 상당한 큰 고통을 주는 악질적인 범행으로 매우 엄격하게 다스리고 있는데, 광고를 한 행동이 성범죄로 언급이 되는 경우는 다른 사람의 성을 사고
-            파는
-            행위, 성매매를 한 상황이라고 할 수 있습니다. 성매매는 금전적인 이익을 가질 목적으로 상대방에 대하여 강제적으로 성적 행위 또는 유사 성적행위를 하는 것을
-            뜻합니다. 성매매 범죄는 계속해서 교묘하게 발생되고 있어 죄질이 매우 좋지 않다고 보고 있는데, 만약 다른 사람의 성을 사고 파는 매매 행위를 하고 불법적인
-            금전을
-            가졌다는 사실이 적발되면 성매매알선 등 행위의 처벌에 관한 법률에 명시하고 있는 형사상의 처벌을 받게 됩니다. 해당 법률은 불법 성매매에 관련한 모든 범행에
-            대한
-            처벌 수위가 규정되어 있는데, 먼저 직접적으로 매매행위를 한 것에는 1년 이하의 징역이나 300만원 이하의 벌금, 구류 또는 과료에 처하게 됩니다. 그리고
-            성매매
-            알선 행위를 하거나 성을 파는 행위를 한 사람을 모집한 사실이 적발되어 범행에 대해 유죄 판결을 받으면 3년 이하의 징역 또는 3천만원 이하의 벌금을 선고
-            받습니다.
-            또, 영업으로 성매매 알선 행위를 하였다면 징역 7년 이하, 벌금 7천만원 이하의 무거운 처벌을 받게 되고, 해당 범행이 행하여지는 업소에 대한 광고를 하거나
-            성을
-            사는 행위를 권유하거나 유인한 광고를 하였다면 3년이하의 징역 또는 3천만원 이하의 벌금에 처하게 됩니다. 이외에도 폭행이나 협박으로 성을 팔게 한 사실에
-            대해서도
-            단체 또는 다중의 위력을 보이는 방법으로 성매매를 강요한 부분에도 모두 법적 처벌을 받도록 하고 있습니다. 한마디로 성매매와 관련되어 있다면 그 어떤 것도
-            넘어가지
-            않고 형사처벌을 받게 됩니다. 만약 성매매를 한 사실이 적발되어 처벌을 받게 될 위기라면 신속히 법적 조력을 요청하여 선처를 받을 수 있도록 해야합니다.
-            성범죄를
-            일으켰다는 사실에 징역 또는 벌금을 받게 되면 형벌과 별도로 보안처분이라는 것이 또 붙게 됩니다. 보안처분은 신상정보등록, 취업제한, 전자발찌부착 등 각종
-            조치들이
-            있는데 이는 모두 실생활에서 크게 영향을 미치기 때문에 자신이 한 범행을 진심으로 반성하여 적극적으로 법적 도움을 받아 성매매 혐의에 대해 선처를 받을 수
-            있도록
-            해야 합니다.​ 18만원을 지불하고 성매매를 2회 한 사실이 적발된 사건 의뢰인은 오피스텔에서 18만원을 내고 성매매를 2회 하였다는 것이 적발되어 성매매
-            혐의에
-            대해 수사기관의 조사를 받게 되었습니다. 의뢰인은 자신의 혐의를 모두 인정하고 있었으나 오피스텔 성매매 범죄가 최근 매우 빈번하게 발생하고 있고 은밀하게
-            범행을 하여
-            엄중하게 다스리고 있는 사안이었습니다. 그래서 엄중한 처벌이 예상되었는데, 변호인은 의뢰인과 일대일로 면담을 하여 사건을 파악하였으며, 그에 대한 대응책을
-            세워
-            나갔고 사건 해결에 필요한 양형 자료를 안내하였으며, 이후 의뢰인에게 양형 자료를 전달 받아 이를 바탕으로 변호인 의견서를 작성하여 수사기관에 제출하였습니다.
-            그리고
-            담당 수사관, 담당 검사와의 면담을 통해 의뢰인이 현재 재범을 하지 않기 위해 노력하고 있음을 전달하고 동시에 최대한 선처를 받을 수 있도록 적극적으로 조력을
-            하였습니다. 그렇게 해서 성매매 혐의에 대하여 기소유예를 받을 수 있게 되었습니다.</t>
+          <t>1. 사실관계 및 쟁점​  의뢰인은
+            지인 및 피해자와 함께 스크린골프를 친 후, 자신의 집에서 술을 마시게 되었습니다. 피해자는 이 술자리에서 상당히 술을 마신 뒤 안방 침대에서 잠이 들었고,
+            의뢰인 역시 상당히 취한 상태에서 평소 자던 공간인 안방 침대에 눕게 되었습니다. 그러나 의뢰인은 당시 안방 불이 꺼져있었고 암막 커튼도 처져있어 이미
+            누워있던 피해자를 발견하지 못했고, 피해자를 확인한 뒤 바로 안방을 나왔습니다. ​  그러나 피해자는 지인에게 가서 "의뢰인이
+            안방에서 잔다"라는 취지로 따졌고, 지인은 피곤하여 피해자의 말을 대수롭지 않게 생각하였습니다. 이에 섭섭함을 느낀 피해자는 언성을 높였고 결국
+            지인과 말다툼을 하다가 112 신고를 하였습니다. 피해자는 112 신고를 받고 출동한 경찰관에게 그제야 의뢰인이 안방 침대에서 자신을 추행하였다는 취지로
+            진술하였습니다. ​  의뢰인은 피해자를 추행한 사실 자체가 없다고 주장하고 있고, 공소사실에 부합하는 증거로는 피해자의 일방적인 진술 뿐인
+            상황에서 피해자 진술의 신빙성을 깨트리는 것이 이 사건의 쟁점이 되었습니다.​2. 본 변호인의 조력 내용​  본 변호인은 증인으로 출석한
+            피해자를 신문한 뒤, 피해자가 최초 피해 진술시부터 증인신문기일에 이르기까지 한 진술을 분석하였습니다. 그 결과, 피해자 진술은 중요 부분에 있어
+            일관적이지도, 구체적이지도 않으며, 오히려 피해자 진술 내용과 상치되는 다른 증거가 다수 존재함을 확인하였습니다. 본 변호인은 재판부에 이런 피해자 진술을
+            그대로 믿을 수 없고, 달리 공소사실을 인정할 다른 증거도 없음을 강조하였습니다.​  그리고 피해자가 처음에는 추행에 관하여 어떠한 언급도
+            하지 않았다가, 지인과 말다툼을 하여 지인 및 의뢰인에 대한 감정이 상한 이후에야 비로소 추행을 당했다고 말한 점을 짚으며, 피해자의 거짓 진술 동기도
+            언급하였습니다.​3. 결과​  재판부는 본 변호인의 주장을 모두 받아들여 의뢰인에 대하여 무죄 판결을 선고하였습니다.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -753,7 +723,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>b389968d-2a98-4fc4-897d-8f42b672a09a</t>
+          <t>e9473717-a12e-43b3-ab10-4dc44edf94e0</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -775,7 +745,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>996325b8-ec67-4040-b132-d90e5db7f74c</t>
+          <t>5bcadcf5-fb21-4732-a737-100a1f0dc0ee</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -785,22 +755,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>22a2ed85-67f8-4cb5-914e-e7f967c7880b</t>
+          <t>01bc6547-387e-49ad-8cbe-39a765a5c9c6</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2024-07-24T16:27:15.492303+09:00</t>
+          <t>2024-07-24T17:09:35.450759+09:00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>[학교폭력전문변호사] 교권침해 아님 성공사례✔</t>
+          <t>전공책을 pdf 스캔만해도 저작권법 위반으로 고소당할까?</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">[학교폭력전문변호사] 교권침해 아님 성공사례✔. </t>
+          <t xml:space="preserve">전공책을 pdf 스캔만해도 저작권법 위반으로 고소당할까?. </t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -853,7 +823,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>996325b8-ec67-4040-b132-d90e5db7f74c</t>
+          <t>5bcadcf5-fb21-4732-a737-100a1f0dc0ee</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -875,22 +845,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>b24ae958-d07d-4653-9813-d462dacff3e3</t>
+          <t>8cc8c7f2-3f07-4139-983c-b61970a0c443</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>996325b8-ec67-4040-b132-d90e5db7f74c</t>
+          <t>5bcadcf5-fb21-4732-a737-100a1f0dc0ee</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dde035fe-3c2e-4850-ae0e-a80ad7f6fa74</t>
+          <t>fbcc3ca4-8fba-4432-9f21-d7532345789a</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2024-07-24T16:27:15.492303+09:00</t>
+          <t>2024-07-24T17:09:35.450759+09:00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -900,76 +870,33 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>들어가며안녕하세요, 안산학교폭력전문변호사
-            이동현변호사입니다.학교폭력은 학생들의 안전과 복지를 심각하게 위협하는 문제로, 사회 전반에 걸쳐 중요한 화두로 떠오르고 있습니다. 이러한 문제를 해결하기 위해
-            법적
-            도움을 제공하는 변호사의 역할은 매우 중요합니다. 이 글의 목적은 학교폭력 사건에서 교권침해가 아닌 성공사례를 통해 변호사의 역할과 중요성을 조명하고,
-            학교폭력과
-            교권침해의 차이점을 명확히 하여 교권을 보호하는 방안을 제시하는 데 있습니다.​학교폭력의 개요학교폭력의 유형과 특징학교폭력은 신체적, 언어적, 심리적 폭력 등
-            다양한
-            형태로 나타납니다. 신체적 폭력은 구타나 협박 등 직접적인 신체적 공격을 포함하여, 언어적 폭력은 욕설, 모욕, 협박 등으로 나타납니다. 심리적 폭력은
-            따돌림, 소문
-            퍼뜨리기, 소셜 미디어를 통한 괴롭힘 등으로 나타날 수 있습니다. 이러한 폭력은 반복적이고 지속적일 때 피해자에게 심각한 영향을 미칩니다.​피해자의 심리적,
-            사회적
-            영향학교폭력의 피해자는 심리적 트라우마, 불안, 우울증 등을 겪을 수 있으며, 학업 성취도 저하, 학교 부적응, 사회적 고립 등의 문제로 이어질 수 있습니다.
-            피해자는 자신감 상실과 자존감 하락을 경험하며, 장기적으로는 성인기까지 영향을 미칠 수 있습니다.​가해자의 법적 책임학교폭력의 가해자는 법적 책임을 질 수
-            있습니다.
-            이는 학교 내 규정에 따른 징계조치뿐만 아니라, 민사 및 형사 소송을 통해 법적 처벌을 받을 수 있음을 의미합니다. 특히, 가해자가 미성년자인 경우 부모나
-            보호자가
-            일정 부분 책임을 질 수 있습니다.​교권침해의 정의와 범위교권침해의 의미교권침해는 교사가 학생이나 학부모, 학교 관리자 등에 의해 부당한 대우를 받거나,
-            교사로서의
-            권리가 침해되는 상황을 의미합니다. 이는 교사의 교육적 권한을 저해하고, 교사의 직업적 존엄성을 훼손하는 행위를 포함합니다.교권침해와 학교폭력의
-            차이점교권침해와
-            학교폭력은 그 대상과 성격이 다릅니다. 학교폭력은 주로 학생 간의 폭력적 행위를 의미하는 반면, 교권침해는 교사를 대상으로 한 부당한 대우를 포함합니다.
-            학교폭력
-            사건에서 교권침해가 발생할 수 있지만, 두 가지 개념은 구별하여 다루어야 합니다.교사의 권리와 보호교사는 교육 현장에서 자신의 권리를 보호받을 권리가
-            있습니다. 이는
-            안전한 교육 환경에서 학생을 교육할 권리, 교육적 판단을 내릴 권리, 그리고 부당한 대우를 받지 않을 권리를 포함합니다. 교사들은 또한 법적 지원을 받을
-            권리가
-            있으며, 필요시 변호사의 도움을 통해 자신의 권리를 보호할 수 있습니다.​사건의 개요 ​고등학생 A양은 같은 반 친구들로부터 심한 집단 따돌림을 당하고
-            있었습니다.
-            이에 A양은 담임선생님에게 여러 차례 도움을 요청하였으나, 담임선생님은 A양에 대해서 "A양이 잘못했다"고 했을 뿐 별다른 도움을 주지
-            않았습니다.
-            그러던 중 A양은 자살을 시도하게 되었고, 이에 A양의 부모님은 A양의 학교폭력 피해 사실을 인지하게 되었습니다. 이후 A양은 전학을 가기로 결정한 뒤
-            가해학생들에
-            대해서 신고를 하는 한편, 전학을 가기로 결정했습니다. A양은 여러 차례 도움을 청했으나 도와주지 않은 담임선생님에 대한 원망과 더 이상 자신과 같은 피해자가
-            발생하지 않게 하기 위해서, 전학을 가기 전에 교장, 교감 선생님에게 담임선생님의 잘못을 말하려고 마음 먹었습니다. A양은 친한 친구 B양과 함께 이야기를
-            하면서 위
-            내용에 대해서 친구들에게 말하며 "담임선생님이 바뀔 수도 있다"는 말을 하게 되었습니다. ​한편, A양의 오빠는 A양으로부터
-            "집단적인
-            따돌림을 당하고 있다"는 사실을 듣고 "사실의 진위 여부를 제대로 확인해 달라", "A양이 담임선생님에게 여러 차례 도움을
-            청했음에도 불구하고 도움을 주지 않았다는 것에 대한 서운한 마음"을 말하기 위해서 담임선생님과 통화를 하게 되었는데, 담임선생님이 "학생이
-            이야기를
-            하지 않아서 몰랐다"는 취지로 말하자, 화가나 다소 감정적으로 담임선생님을 대하게 되었습니다. 그러자 담임선생님은 연락을 차단하였습니다. 이에 A양의
-            오빠는
-            담임선생님과 더 이상 연락이 되지 않자 '담임선생님의 책임을 묻겠다'는 취지로 담임선생님에게 "언론과 교육청이 정식으로 문제를
-            삼겠다"는 메시지를 보내게 되었습니다. ​그로부터 며칠 뒤 A양와 A양의 오빠는 교육활동 침해 행위로 신고가 되었다는 사실을 연락받게
-            되었습니다.​A양의
-            위기​A양은 같은 반 학생들로부터 집단적으로 따돌림을 당한 것 뿐만 아니라 담임선생님으로부터 교권침해로 신고를 당해 정신적으로 엄청난 고통을 받게
-            되었습니다.​이에
-            A양과 A양의 부모님은 어떻게 대응해야 할지 고민하던 중 교권침해전문변호사인 저를 찾아오셨습니다.​'교육활동 침해 아님' 결정​저는 이 사건을
-            수임한
-            뒤 관련된 자료를 꼼꼼하게 검토하였습니다.​그런 뒤 저는 여러 객관적인 자료를 바탕으로, A양에 대해서, 'A양이 친구들에게 "담임선생님이
-            바뀔 수
-            있다" 등이라고 말한 것은 법률에 규정된 교육활동 침해 행위에 해당하지 않는다'는 점, A양의 오빠에 대해서는, '담임선생님이 연락을
-            차단하자
-            이에 대해서 문제를 삼겠다는 취지로 말했을 뿐, 협박 등의 언사를 한 사실이 전혀 없으므로 교육활동 침해를 한 사실이 전혀 없다'는 점 등을 적극적으로
-            어필하는 내용의 의견서를 제출하는 한편, 지역교권보호위원회에 출석해 위 내용에 대해서 적극적으로 어필하였습니다.​결국 이러한 주장을 받아들여, 지역교권위원회는
-            A양과
-            A양의 오빠에 대해서 "교육활동 침해 아님" 결정을 내렸습니다. ​교권침해전문변호사의 조력이 필요한 이유​최근 사회적으로 교권침해가 이슈가
-            되고
-            있어, 자칫 잘못 대응하였다가 억울하게 처분을 받거나 사안에 비해 중한 처분을 받을 수 있어 주의해야 합니다. 교권침해는 교사 개인의 문제를 넘어 교육 환경
-            전체에
-            영향을 미치는 중대한 사안입니다. 특히, 교사들은 자신의 권리를 보호하기 위한 법적 지식과 경험이 부족할 수 있기 때문에, 잘못된 대응은 상황을 악화시킬
-            위험이
-            큽니다.​따라서 교권침해가 문제된 경우, 혼자서 문제를 해결하려 하기보다 사건 초기부터 다양한 교권침해 사건을 다루어 본 안산학교폭력전문변호사 의 이동현
-            변호사의
-            도움을 받는 것이 매우 중요합니다. 교권침해전문변호사는 사건의 특성과 법적 절차를 정확히 이해하고 있으며, 교사의 권리를 보호하기 위해 최적의 전략을
-            제공합니다.
-            안산학교폭력전문변호사 이동현변호사는 교사의 상황을 철저히 분석하고, 필요한 증거를 수집하며, 법적 절차를 대리하여 교사의 권리를 최대한 보장받을 수 있도록
-            돕습니다.​교권침해는 단순히 법적 문제를 넘어서, 교사의 교육적 권한과 존엄성을 지키는 중요한 문제입니다. 안산학교폭력전문변호사의 도움을 받아 교권침해에
-            효과적으로
-            대응함으로써, 교육의 질을 향상시키고, 학생들에게도 긍정적인 영향을 미칠 것입니다.​</t>
+          <t>Focus ON - 전공책을 pdf 스캔만해도
+            저작권법으로 고소당할까?강의를 듣는 학생과 직장인이라면 필히 교재를 구매해야합니다. 교재비가 만만치 않아 지인을 교재를 빌려 복사집에서 복사를 한다던지 (속칭
+            ‘제본뜨기’), 교재pdf파일을 당근이나 에타에서 거래하는 방법을 생각해보셨을텐데요. 경우에 따라 저작권침해로 처벌받을 수 있다는 사실 알고 계셨나요? 교재를
+            항상 들고 다니기에는 너무 무거워서 pdf파일로 변환하여 태블릿에 저장해서 다니는 경우도 많다는데. 어떤 경우에 저작권법 위반에 해당하는지 자세히
+            알아보겠습니다.시끌법적 영상으로 확인하기 - '전공책 pdf 스캔' 고소감인 이유출처 : 시끌법적 영상 캡처아이패드로 전공수업 들을 때 책
+            pdf 파일로 만드는 법1번 어플로 스캔한다2번 복사집에 맡긴다둘 중 하나는 불법입니다. 어떤 걸까요?&amp;nbsp;최근 대학생들이 로톡에 많이
+            올린 상담글에타에서 전공책 PDF를 팔았다가 고소당했다는 내용!하나에 겨우 몇천 원, 심지어는 기프티콘 한 장에 팔았더라도요불법 복제본 판매는 저작권
+            침해!민형사상 책임을 지게 됩니다합의금은 보통 수백만 원 선, 합의를 못하면 벌금형이나 기소유예를 주로 받는데요. 기소유예는 전과는 남지 않지만, 군인 등
+            일부 직업군의 취업 신원조회에 걸릴 수 있고요. 캐나다 등 까다로운 나라의 비자발급 불이익을 받습니다.책을 PDF로 복제하면 반드시 나 혼자! 개인적으로 써야
+            하는데요. ‘사적 이용'은 법적으로 허용되기 때문!하지만, “다만”으로 시작하는 이 조문에 따라(저작권법 제30조) 복사업체에 의뢰하는 건 불법입니다!
+            본인이 직접 복제해서 써야 하죠.또, 시험기간에 많은 ‘족보' 찾는 글!선후배 사이 돈 안 받고 공유해도 저작권 침해가 성립하고요. 교수님 강의
+            몰래&amp;nbsp;녹음한 파일 공유도 마찬가지! 강의도 소설, 시처럼‘어문 저작물'에 해당, 허락 없이 공유하면 안 됩니다.시끌법적 영상으로
+            보기 &amp;gt;&amp;gt; 저작권법 제 30조제30조(사적이용을 위한 복제)공표된 저작물을 영리를 목적으로 하지 아니하고 개인적으로
+            이용하거나 가정 및 이에 준하는 한정된 범위 안에서 이용하는 경우에는 그 이용자는 이를 복제할 수 있다. 다만, 공중의 사용에 제공하기 위하여 설치된
+            복사기기, 스캐너, 사진기 등 문화체육관광부령으로 정하는 복제기기에 의한 복제는 그러하지 아니하다.제46조(저작물의 이용허락)①저작재산권자는 다른 사람에게 그
+            저작물의 이용을 허락할 수 있다.②제1항의 규정에 따라 허락을 받은 자는 허락받은 이용 방법 및 조건의 범위 안에서 그 저작물을 이용할 수 있다.③제1항의
+            규정에 따른 허락에 의하여 저작물을 이용할 수 있는 권리는 저작재산권자의 동의 없이 제3자에게 이를 양도할 수 없다.제136조(벌칙)① 다음 각 호의 어느
+            하나에 해당하는 자는 5년 이하의 징역 또는 5천만원 이하의 벌금에 처하거나 이를 병과(倂科)할 수 있다. [개정 2011. 12. 2., 2021. 5.
+            18.]&amp;nbsp;&amp;nbsp;1. 저작재산권, 그 밖에 이 법에 따라 보호되는 재산적 권리(제93조에 따른 권리는 제외한다)를
+            복제, 공연, 공중송신, 전시, 배포, 대여, 2차적저작물 작성의 방법으로 침해한 자&amp;nbsp;&amp;nbsp;2.
+            제129조의3제1항에 따른 법원의 명령을 정당한 이유 없이 위반한 자②다음 각 호의 어느 하나에 해당하는 자는 3년 이하의 징역 또는 3천만원 이하의 벌금에
+            처하거나 이를 병과할 수 있다. [개정 2009. 4. 22., 2011. 6. 30., 2011. 12.
+            2.]&amp;nbsp;&amp;nbsp;1. 저작인격권 또는 실연자의 인격권을 침해하여 저작자 또는 실연자의 명예를 훼손한 자교재를 직접
+            스캔하려면 시간과 수고가 발생하다보니 전문 복사 업체에 맡겨 스캔하는 것을 생각해 볼 수도 있는데, 이 경우는 복제행위를 하는 주체가 본인이 아니기 때문에
+            처벌될 수 있습니다. 또한, 직접 집에서 스캔한 PDF파일을 온라인에 무료로 게시하는 것도 ‘저작권법 제 30조’의 개인적으로 이용하는 것이라고 볼 수 없기
+            때문에 법에서 허용된 사적 복제에 해당하지 않습니다.그렇다면, 여러명이 교재를 1/N로 공동구매하여 스캔한 다음, 공동으로 나누어가지는 것은 저작권법침해,
+            저작권법 위반일까요? 로톡 상담 사례로 확인해보겠습니다.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1022,7 +949,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>996325b8-ec67-4040-b132-d90e5db7f74c</t>
+          <t>5bcadcf5-fb21-4732-a737-100a1f0dc0ee</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1036,6 +963,4971 @@
         </is>
       </c>
       <c r="T5" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>769e7db3-57b3-4347-8e83-2171fade1fe5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>3c9b4d89-fd04-4ee6-bca3-d167aefd18d8</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.450759+09:00</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>부부각서 내용대로 이혼할 수 있을까요?</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부부각서 내용대로 이혼할 수 있을까요?. </t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>prompter</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>769e7db3-57b3-4347-8e83-2171fade1fe5</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6e91d26f-eb91-4128-be36-842006203a33</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>769e7db3-57b3-4347-8e83-2171fade1fe5</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>cb57f234-8ea2-4d03-9edb-f4b4d93250d5</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.450759+09:00</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>​이혼각서, 부부각서로 작성한 내용대로 이혼할 수
+            있을까요? 사례를 통해 함께 알아보겠습니다.안녕하세요. 이혼 및 가사법 전문 임은지 변호사입니다. 부부 사이에 문제가 생기게 되면 미래의
+            이혼에 대비하여 부부각서를 쓰게 되는 때가 있습니다. 예를 들면, 배우자의 불륜으로 이혼하게 될 시 모든 재산을 포기하고 이혼한다는 내용을 담은 부부각서
+            내지는 이혼각서를 작성하게 되는 경우인데요. 그러면, 차후 이혼하게 되었을 때 각서의 내용대로 이혼할 수 있을까요? 정답은, 그렇지
+            않습니다. ‍ 구체적 사례를 통해 알아보도록 하겠습니다.‍ 부부각서의 효력 (서울가정법원 2016. 8.
+            16. 선고 2014드합3184 (반소: 2014드합305279) 판결)판결 속 부부는 이혼에 대비해 재산분할, 위자료, 양육비에 관한 이혼 각서를 작성하고
+            공증을 받았습니다. 몇 년  후 부부관계가 악화하여 이혼에 따른 재산분할, 위자료, 양육비에 대한 소송을 진행하게 됐는데요. 법원에서는 각서의
+            내용 그대로 판결을 내려주지 않았습니다.법원에서는 부부가 이혼 각서를 작성했다는 사실만을 확인했을 뿐입니다. 즉, 부부사이에 문제가 생겨 차후 문제가 생겨
+            이혼할 경우를 대비하여 작성한 '이혼각서' 내지는 '부부각서', '재산포기각서' 등이 법적 효력이 없다는 것을 알
+            수 있습니다.‍ 부부각서는 재판 시 참고자료로 쓰입니다.결혼 생활 중 문제로 인하여 작성한 부부각서는 재판 시 이혼에 대한 책임이 누구였는지, 부부간 어떤
+            문제가 있었는지를 가늠하는 참고  자료로 쓰입니다. 공증을 받았어도  그 자체로 법적 효력을 발생하기는 어렵습니다. 따라서
+            부부각서를 작성하시게 된다면 이 점을 꼭 참고하여 주시면 좋겠습니다.부부간 문제로 이혼각서를 작성하였고, 이후 같은 문제가 발생하여 이혼하시게 될 때 이를
+            신뢰하시고 이혼을 진행하시기 보다는 이혼 과정에서 전문변호사의 조력을 통해 이혼각서를 효과적으로 주장하여 나에게 유리한 판결을 내리는데 보조적인 역할을 할 수
+            있도록 하는 것이 중요합니다. 따라서 결혼생활의 어려움으로 이혼을 준비 중이시라면 상담을 꼭 받아보시기 바랍니다. 감사합니다.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>assistant</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>769e7db3-57b3-4347-8e83-2171fade1fe5</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>d25e123b-d4d4-4197-9005-e2e5c88810d0</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>8adcd7ea-ecc0-4d92-b46f-07bde884ea34</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.450759+09:00</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>헬스/피트니스/필라테스 환불 금액은 얼마일까</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">헬스/피트니스/필라테스 환불 금액은 얼마일까. </t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>prompter</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>d25e123b-d4d4-4197-9005-e2e5c88810d0</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>86f99d36-3b4e-4a6c-8423-f07673dd6d48</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>d25e123b-d4d4-4197-9005-e2e5c88810d0</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>79349e18-11e7-4e65-b3f5-31d8caf2e1bb</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.451757+09:00</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>지인들로부터 가장 많이 상담오는 유형 중에 하나인데
+            헬스장, 피트니스, 골프연습장, 필라테스 등 운동 시설을 장기간 등록했다가 도중에 그만두고 환불받으려고 할 때 그 환불금액에 항상 입장차이가 있다.1. 어떤
+            법률이 적용되는지위와 같은 사건은 방문판매 등에 관한 법률(약칭: 방문판매법)의 적용을 받는다. 웬 방문판매법...? 이라고 생각할 수 있겠으나 방문판매
+            '등'에 관한 법률이고 아래와 같이 방문판매법상 계속거래에 해당하기 때문에 이 법이 적용되는 것이다. 계속거래에 관한 내용은 제30조 ~
+            제34조에 규정되어 있다.방문판매법 제2조(정의)10. “계속거래”란 1개월 이상에 걸쳐 계속적으로 또는 부정기적으로 재화등을 공급하는 계약으로서 중도에
+            해지할 경우 대금 환급의 제한 또는 위약금에 관한 약정이 있는 거래를 말한다.2. 해지권의 존재원래 개인 사이에 계약을 맺었으면 별도로 해제,해지 사유가
+            발생하지 않는 이상 한 쪽 마음대로 계약을 종료할 수 없다. 그러나 아래와 같이 31조에서 언제든지 계약을 해지할 수 있다고 규정하고 있기 때문에 계약
+            중간이라도 언제든 해지하겠다는 의사표시만 하면 즉시 계약은 종료된다.단, 업체측 잘못 없이 소비자가 일방적으로 그만두는 것이기 때문에 일정 금액 위약금을
+            지급해야 한다.방문판매법 제31조(계약의 해지)계속거래업자등과 계속거래등의 계약을 체결한 소비자는 계약기간 중 언제든지 계약을 해지할 수 있다. 다만, 다른
+            법률에 별도의 규정이 있거나 거래의 안전 등을 위하여 대통령령으로 정하는 경우에는 그러하지 아니하다.3. 어떤 업종에 적용되는지가. 계약 해지 시 발생하는
+            위약금이나 반환해야 할 금액에 관한 내용은 방문판매법 제32조에 규정되어 있지만 구체적인 산정기준은 고시(계속거래 등의 해지·해제에 따른 위약금 및 대금의
+            환급에 관한 산정기준)를 통해 정하고 있다.나. 해당 고시 제3조를 보면 듀오 같은 국내결혼중개업, 인터넷 강의(인강)를 제공하는 컴퓨터 통신교육업, 헬스,
+            피트니스, 요가, 필라테스, 미용업, 학습지업에 적용된다.4. 위약금은 얼마인지위 산정기준 고시에 따르면 위약금은 아래와 같이 결혼중개업은 20%, 그 외
+            다른 업종은 10%의 위약금이 발생한다.5. 이용횟수, 기간에 따른 공제액은 얼마인지이 부분이 많이들 헷갈리는데, 고시 제5조 제1항에 따르면계속거래 등의
+            해지·해제에 따른 위약금 및 대금의 환급에 관한 산정기준 제5조 제1항소비자는 사업자에게 지급한 계약대금에서 계약의 해지 또는 해제의 의사표시가 사업자에게
+            도달한 시점까지 공급받은 단위에 해당하는 단위대금, 부가상품의 가액, 제4조에 따른 위약금을 공제한 나머지의 환급을 청구할 수 있다.쉽게 말하면 소비자가
+            지급한 금액 - 위약금 - 해지 시점까지 이용금액 에 해당하는 금액을 돌려받을 수 있다.예를 들어 100만원에 5개월의 헬스 이용권을 샀는데 1달 이용 후
+            해지하는 경우, 위약금 10만원(10%), 한 달 이용했으므로 약 20만원(더 정확히는 일수를 따져서 해야한다) 이므로 30만원을 공제한 70만원을 받을 수
+            있는 것이다.만약 개인PT 30회를 끊었고 실제로는 10번만 갔다면, 역시 10% 위약금과 총 지급한 금액의 1/3만 제외하고 돌려받을 수 있는 것이다.6.
+            정상가 공제 가능한지가. 그런데 많은 헬스장 등 운동시설에서는 결제시 이벤트 가격으로 결제하더라도 환불할 때는 '정상가'를 적용하여 공제한다고
+            계약서에 기재한다. 이 문구 때문에 가격차이가 확 생기게 되고 법적 쟁점 역시 확 늘어난다.나. 약관규제법 준수 여부1) 대부분 헬스장 등 운동시설에서는 미리
+            작성된 계약서로 고객과 계약한다. 그렇다면 해당 계약서는 약관에 해당되고 약관의 규제에 관한 법률(약칭:약관법)의 적용을 받는다. 사건 해결에 필요한 주요
+            조항은 아래와 같다.제3조 약관의 작성 및 설명의무② 사업자는 계약을 체결할 때에는 고객에게 약관의 내용을 계약의 종류에 따라 일반적으로 예상되는 방법으로
+            분명하게 밝히고, 고객이 요구할 경우 그 약관의 사본을 고객에게 내주어 고객이 약관의 내용을 알 수 있게 하여야 한다.③ 사업자는 약관에 정하여져 있는 중요한
+            내용을 고객이 이해할 수 있도록 설명하여야 한다. 다만, 계약의 성질상 설명하는 것이 현저하게 곤란한 경우에는 그러하지 아니하다.④ 사업자가 제2항 및
+            제3항을 위반하여 계약을 체결한 경우에는 해당 약관을 계약의 내용으로 주장할 수 없다.(=무효다)제5조 약관의 해석② 약관의 뜻이 명백하지 아니한 경우에는
+            고객에게 유리하게 해석되어야 한다.제6조(일반원칙)① 신의성실의 원칙을 위반하여 공정성을 잃은 약관 조항은 무효이다.② 약관의 내용 중 다음 각 호의 어느
+            하나에 해당하는 내용을 정하고 있는 조항은 공정성을 잃은 것으로 추정된다.1. 고객에게 부당하게 불리한 조항2. 고객이 계약의 거래형태 등 관련된 모든 사정에
+            비추어 예상하기 어려운 조항3. 계약의 목적을 달성할 수 없을 정도로 계약에 따르는 본질적 권리를 제한하는 조항제9조(계약의 해제ㆍ해지)계약의 해제ㆍ해지에
+            관하여 정하고 있는 약관의 내용 중 다음 각 호의 어느 하나에 해당되는 내용을 정하고 있는 조항은 무효로 한다.1. 법률에 따른 고객의 해제권 또는 해지권을
+            배제하거나 그 행사를 제한하는 조항4. 계약의 해제 또는 해지로 인한 원상회복의무를 상당한 이유 없이 고객에게 과중하게 부담시키거나 고객의 원상회복 청구권을
+            부당하게 포기하도록 하는 조항2) 내용이 많아 어려운데 차차 살펴보면, 계약서에 정상가 차감한다고 적어 놓더라도 만약 그것을 고객에게 설명하지 않았다면
+            무효이고 위에서 본 방식대로 계산해서 돌려줘야 한다. 소송을 하게 되면 고객에게 해당 내용을 설명하였음을 업체측에서 증명해야 한다.3) 또 간혹 이벤트가로
+            결제한 경우 환불이 불가능하다고 적는 곳도 있는데 역시 법률(방문판매법)에 따른 고객의 해지권을 배제하는 조항이어서 무효이다. 즉 액수가 문제이지 환불 자체는
+            무조건 가능하다.다. 잘 설명했다면 정상가 차감이 가능한지판례를 여러 검색어로 많이 찾아봤는데 보통 다투는 금액이 소액이어서 소송까지 잘 가지 않아 판례
+            숫자가 적다. 현재 대법원 판례는 없는 것으로 보이고 2심 판례 두 개가 입장이 나뉜다.1) 정상가 차감 가능하다는 판례이에 대하여 원고는 피고의 헬스장
+            이용약관이 약관의 규제에 관한 법률 제8조와 방문판매 등에 관한 법률 제31조에 위반하여 효력이 없다고 주장하나, ... 이 사건 이용권은 1년분 헬스장
+            이용료를 선급하는 대신 정상요금보다 할인된 가격에 헬스장을 이용할 수 있게 한 것으로, 그에 미치지 못하는 기간으로 헬스장을 이용하고자 하는 경우 위와 같은
+            가격 할인 혜택을 제공하지 않는 것이 불합리하거나 부당하다고 하기는 어려운 점을 감안하면, 원고의 주장을 인정할 별다른 사정이 보이지 아니하므로 위 주장은
+            이유 없다.쉽게 말해 장기간 이용하는 대신 단위당 가격을 싸게 해줬던 것이니, 계약기간 보다 적게 이용할 경우 정상가를 기준으로 차감해야 한다는 판결이다.다만
+            해당 판결에서 원고가 약관규제법과 방문판매법 31조만 주장했는데 방문판매법상 소비자에게불리한계약의 효력없음 조항까지 주장했다면 어떨까 하는 아쉬움도 있다.
+            변호사 없이 혼자 소송하셔서 관련 법률을 모두 주장하지는 않았던 것 같다. 판사는 당사자의 주장이 없으면 법이 있어도 그렇게 판단할 수가 없다.2) 소비자가
+            지급한 가격을 기준으로 차감해야 한다는 판례계약서는 약관에 해당하는데,1 할인하여 판매된 상품이라는 이유만으로 일률적으로 계약해지로 인한 고객의
+            원상회복청구권을 포기시키고 있고,2 계약금액을 기준으로 환불금 정산을 하는 것이 통상적이며, 3 PT 계약은 특정 금액을 '정가'로 규정해 놓고
+            상시 각종 명목으로 그보다 인하한 금액으로 계약을 체결하여, 정가가 추상적인 개념으로만 존재하고 액수가 부풀려 질 가능성이 높으며 고객의 입장에서는 애초
+            할인가 자체를 기준으로 삼고 계약을 체결하는 경우가 대다수인 점 등을 고려하면, 고객이 계약의 거래형태 등 관련된 모든 사정에 비추어 예상하기 어렵고, 계약의
+            해지로 인한 고객의 원상회복청구권을 부당하게 포기하도록 하는 조항으로서 약관법 제6조 제1항 및 제2항 제2호, 제9조 제4호에 따라 무효이다.쉽게 말해
+            이벤트 가격이라고 하지만 사실 1년 내내 각종 명목(신년, 방학, 명절 등등 많을 것이다)으로 할인 판매 하고 있으니 정가는 실제로는 쓰이지 않는 것이고
+            사실상 환불을 부당하게 포기하도록 하는 것이므로 무효라는 것이다.위 재판은 원고측에 변호사님이 선임되어 진행되었다 보통 소액이라 변호사를 선임하기로 결정하기
+            쉽지 않은데 대체 어떤 사정이 있었을지...3) 공교롭게도 위 두 판례 모두 2021년에 선고된 것이다. 관련된 여러 판례들은 헬스장측이 설명을 했다는 증거가
+            없다는 판결 등 다양하지만 전체적인 분위기는 정상가 차감은 안되고 소비자가 실제 지급한 금액을 기준으로 횟수에 맞는 금액을 차감하는 것이 맞다는 쪽으로
+            느껴진다.7. 형사처벌의 가능성방문판매법에는 업체측에 대해 형사처벌에 관한 규정도 두고 있다.제34조(금지행위 등) ① 계속거래업자등은 다음 각 호의 어느
+            하나에 해당하는 행위를 하여서는 아니 된다.1. 계속거래등의 계약을 체결하게 하거나 계약의 해지 또는 해제를 방해하기 위하여 소비자를 위협하는 행위2. 거짓
+            또는 과장된 사실을 알리거나 기만적 방법을 사용하여 소비자를 유인 또는 거래하거나 계약의 해지 또는 해제를 방해하는 행위3. 계속거래등에 필요한 재화등을
+            통상적인 거래가격보다 현저히 비싼 가격으로 구입하게 하는 행위4. 소비자가 계속거래등의 계약을 해지 또는 해제하였는데도 정당한 사유 없이 이에 따른 조치를
+            지연하거나 거부하는 행위5. 계약의 해지 또는 해제를 방해할 목적으로 주소ㆍ전화번호 등을 변경하는 행위6. 분쟁이나 불만 처리에 필요한 인력 또는 설비가
+            부족한 상태를 상당 기간 방치하여 소비자에게 피해를 주는 행위7. 소비자의 청약이 없는데도 일방적으로 재화등을 공급하고 재화등의 대금을 청구하는 행위8.
+            소비자가 재화를 구매하거나 용역을 제공받을 의사가 없음을 밝혔는데도 전화, 팩스, 전자우편 등을 통하여 재화를 구매하거나 용역을 제공받도록 강요하는 행위다음
+            각 호의 어느 하나에 해당하는 자는 2년 이하의 징역 또는 5천만원 이하의 벌금에 처한다.주로 해지하고 환불요청 했음에도 불구하고 시간을 끄는 4호로 자주
+            처벌받게 된다.이렇게 헬스장 등 운동시설 환불관련 쟁점을 얼추 다 정리해 놓았다. 환불을 다 받을 수 있는 법적 권리가 있다고 해도 이를 실제로 실현하는 데는
+            들인 돈에 비해 너무 많은 시간이나 비용이 소모되니 참 아쉬운 부분이다.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>assistant</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>d25e123b-d4d4-4197-9005-e2e5c88810d0</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>597d5467-4563-4d6d-863e-3705d46e19f5</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>fb5c8aa5-f90b-4188-b9cb-871664e37cde</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.451757+09:00</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>상속재산분할협의를 원인으로 한 약정금 청구</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상속재산분할협의를 원인으로 한 약정금 청구. </t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>prompter</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>597d5467-4563-4d6d-863e-3705d46e19f5</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3587ef8c-b976-4457-873e-4ac98ba7dfaa</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>597d5467-4563-4d6d-863e-3705d46e19f5</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>4b2e9bdd-4032-4644-a9f9-72be2d7243df</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.451757+09:00</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>상속재산분할협의를 원인으로 한 약정금 청구(청구금액의
+            90프로 감액)​​​ 안녕하세요. 조수영 변호사입니다.​ 요즘 상속문의가 더욱 많아지고 있습니다. 오늘은 상속재산분할협의를 원인으로 한 약정금 청구 소송에서
+            상대방이 청구한 청구금액의 90프로를 감액한 것으로 조정이 성립된 사례를 소개해드리겠습니다. ​​1. 의뢰인에게 상속재산분할협의를 근거로 1억원이 청구됨​​
+            의뢰인은 혼인기간 10년의 아내로, 남편과 혼인생활을 하고 있었습니다. 그런데 어느날 갑자기 교통사고로 인해 남편이 별세하게 되었고, 매우 큰 충격에 빠지게
+            되었습니다.​​ 의뢰인은 장례식을 치른 후 남편 명의 아파트를 처분하려고 했습니다. 의뢰인과 남편간에는 아이가 없어 시부모님이 상속인이었습니다. 의뢰인은 남편
+            명의 아파트를 단독으로 보유하고 남편 채무도 정산하는 것으로 정리하려고 하였습니다. 의뢰인은 이후 남편 명의 아파트를 처분한 후 모든 채무를 정산했습니다.
+            그런데 몇 달 후 시부모님이 의뢰인에게 매각 대금 중 본인들의 상속분 1억원을 요구하였습니다. ​​2. 의뢰인이 남편 명의 재산은 전부 가지는 것으로
+            협의하였다고 주장함​​ 이 사건은 곧바로 조정기일이 지정되었습니다. 저는 의뢰인을 대리하여,​​1) 의뢰인과 시부모님간에는 사전에 의뢰인이 남편 명의 재산을
+            전부 갖기로 협의되었으며,​​2) 의뢰인과 남편은 혼인기간이 10년되었었고 맞벌이를 했기 때문에 남편 명의 재산의 50프로는 의뢰인의 것이 될 수
+            있고,​​3) 상속소송에서 아내 기여분이 50프로 이상 인정된 판례가 있다는 것,​​을 주장하였습니다. ​​​3. 청구금액의 90프로를 감액함​​ 위와 같이
+            주장한 결과,​​1) 의뢰인이 원고들(시부모)에게 1천만원을 지급하고,​​2) 원고들은 앞으로 의뢰인에게 어떠한 민,형사상 소송을 제기하지 않는다는
+            부제소특약을 기재하는 것,​​​으로 마무리될 수 있었습니다.​ 이 사건의 경우 원고들이 청구한 금액 90프로를 감액하고, 원고들이 이후 민,형사소송을 제기하지
+            않는 것으로 원만히 조정하였다는 점에서 상당히 의미가 있었던 사건이었습니다. ​</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>assistant</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>597d5467-4563-4d6d-863e-3705d46e19f5</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>7b3ebe32-c284-4c34-bfb5-a4265d5caaf5</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>a0045020-e29c-4563-b59d-250ee602f289</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.451757+09:00</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>연인 간 성범죄 성립 가능할까?</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">연인 간 성범죄 성립 가능할까?. </t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>prompter</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>7b3ebe32-c284-4c34-bfb5-a4265d5caaf5</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ead95700-aa33-47f5-899d-719bd2bdb59e</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>7b3ebe32-c284-4c34-bfb5-a4265d5caaf5</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>5ab2bb26-c7fc-4208-8735-98521ad21f30</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.451757+09:00</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>들어가며​안녕하세요. 저는 수백 건의 성범죄 사건에서
+            무죄, 무혐의, 기소유예 등 많은 좋은 결과를 도출해 낸 성범죄전문변호사입니다.​성범죄는 개인의 신체적, 정신적 자유를 침해하는 심각한 범죄로, 사회의 법적,
+            윤리적 기준에 부합하지 않는 행윕니다. 특히 연인 간 성범죄는 사랑과 신뢰의 관계에서 발생하는 복잡한 문제로, 단순한 오해나 갈등이 아니라 법적으로 명확한
+            범죄가 될 수 있습니다. 이 글에서는 연인 간 성범죄의 가능성을 법적 관점에서 분석하고, 동의와 강제의 경계, 판례 등을 통해 연인 관계에서 성범죄가 어떻게
+            성립할 수 있는지를 살펴보겠습니다.​연인 간 성범죄의 논의는 단순히 개인적 문제에 그치지 않고, 법적, 사회적 시각에서 중요한 의미를 갖습니다. 많은 경우,
+            피해자는 범죄를 인정하지 않거나 신고를 주저하는 경우 많아, 법적 대응과 처벌이 어려울 수 있습니다. 이 글에서는 연인 간 성범죄의 법적 기준을 명확히 하고,
+            이를 해결하기 위한 법적 절차와 지원 시스템에 대해서도 논의할 것입니다.​성범죄 처벌?성범죄는 대표적으로 '강간죄',
+            '강제추행죄' 등이 있습니다.​강간죄, 강제추행죄는 '형법'이 적용되어, 강간죄는 3년 이상의 유기징역에, 강제추행죄는 10년
+            이하의 징역 또는 1,500만 원 이하의 벌금에 처해집니다.​​성범죄의 정의와 법적 기준성범죄는 특정한 성적 행위가 동의 없이 이루어지는 경우를 포함하는
+            범죄로, 대한민국 형법에서는 성범죄를 다음과 같이 정의합니다​​형법 제297조(강간) : '강간'은 다른 사람의 성기를 강제로 삽입하는 행위를
+            의미하며, 이때 피해자가 동의하지 않거나 저항할 수 없는 상태일 때 성립합니다.형법 제298조(강제추행) : '강제추행'은 타인의 신체에 대해
+            성적 의도를 가지고 강제로 접촉하거나 행위를 하는 것을 의미합니다.​성범죄가 성립하기 위해서는 다음과 같은 법적 기준을 충족해야 합니다​동의의 부재피해자가
+            행위에 대해 명시적이거나 묵시적인 동의를 하지 않았거나, 동의를 철회했음에도 불구하고 행위가 계속된 경우에 성범죄가 성립할 수 있습니다.강제성피해자가 신체적,
+            정신적 강제로부터 벗어날 수 없는 상태에서 행위가 이루어져야 합니다. 여기에는 물리적 폭력뿐만 아니라, 심리적 압박이나 협박도 포함됩니다.행위의 성적
+            성격행위가 성적 목적을 가지고 이루어진 경우, 즉 성적 만족을 추구하거나 성적 접촉이 포함된 경우 성범죄로 간주됩니다.​연인 간의 성적 행위가 법적 성범죄로
+            인정되기 위해서는, 연인 관계에서도 동의와 강제의 기준이 엄격히 적용됩니다. 따라서 연인 간의 성적 행위가 법적으로 성범죄로 간주되기 위해서는 동의가 명확히
+            부재하거나, 피해자가 적극적으로 저항할 수 없는 상태에서 이루어진 경우에 해당합니다.​성범죄의 법적 기준을 이해하는 것은 연인 간의 성범죄를 파악하고 대응하는
+            데 중요합니다. 법적 기준을 바탕으로 피해자가 보호받을 수 있는 방법과 법적 절차를 이해하는 것이 필요합니다.연인간 성범죄가 성립 가능할까?​연인간 성범죄가
+            성립가능한지 문의를 하시는 분들이 많으나, 연인 사이에도 상대방의 의사에 반하여 강제로 신체적 접촉을 하거나 성관계를 하게 되면 강제추행, 강간죄가 성립하게
+            됩니다. ​성범죄는 피해자의 성적 자기결정권을 보호하기 위한 것이기 때문에, 의사에 반하는 신체적 접촉, 성관계를 범죄에 해당할 수 있습니다. 따라서
+            연인간이라고 할지라도 상대방의 의사를 정확하게 확인한 뒤 서로 합의가 된 상태에서 신체적 접촉이나 성관계를 해야 하며, 상대방이 거부의사를 표시하였다면 신체적
+            접촉이나 성관계를 하면 안 됩니다. 이는 명백히 범죄에 해당합니다.​최근 연인간에 헤어지는 과정에서 성범죄로 고소를 당하는 경우가 많은데, 억울한 경우에는
+            피해자와 주고받은 메시지 내용, 모텔 혹은 집 주변의 CCTV 영상 등 여러 객관적인 자료를 바탕으로 피해자와 서로 합의하에 신체적 접촉 혹은 성관계를
+            하였다는 점, 피해자가 헤어지는 과정에서 다소 악의적으로 신고를 했을 가능성이 있다는 점 등을 어필해야 하며, 실제 상대방의 의사에 반하여 강제추행, 강간을
+            저지른 경우에는 반성문, 탄원서, 합의서, 정신과 진료 내역서 등 다양한 양형자료를 바탕으로 반성하고 있다는 점, 피해자와 합의하였다는 점, 초범이라는 점
+            등을 주장하며 최대한 선처를 해달라고 어필해야 원하는 결과를 얻을 수 있습니다.​그러나 이 모든 것을 혼자서 판단하고 대응하기에 어려움이 있을 수 있으므로
+            성범죄전문변호사의 도움을 받는 것이 반드시 필요합니다. ​실무적 고려사항연인 간 성범죄 사건을 다루는 것은 법적, 윤리적, 심리적 측면에서 복잡한 문제를
+            동반합니다. 법률 전문가로서 이와 같은 사건을 처리할 때 고려해야 할 실무적 사항은 다음과 같습니다.​(1) 변로사로서의 조언과 전략사건의 전체적인 이해 :
+            사건을 맡기 전, 사건의 모든 배경과 경과를 면밀히 조사해야 합니다. 피해자와 피고인의 진술, 사건의 정황, 증거 등을 종합적으로 검토하여 사건의 본질을
+            파악하는 것이 중요합니다.법적 전략 수립 : 사건의 성격에 따라 적절한 법적 전략을 수립해야 합니다. 연인 간의 관계에서 성범죄를 주장하는 경우, 동의의
+            여부와 강제성의 입증이 핵심이므로, 이에 대한 전략을 명확히 해야 합니다. 예를 들어, 피해자의 동의 부재를 입증하기 위해 필요한 증거를 확보하거나, 법적
+            공방에서의 접근 방식을 정리할 필요가 있습니다.피해자와의 신뢰 구축 : 피해자와의 관계를 신뢰 기반으로 형성하는 것이 중요합니다. 피해자는 심리적으로 취약할
+            수 있으므로, 정서적 지원과 법적 조언을 신중하 제공해야 합니다.​(2) 연인 간 성범죄 사건을 다룰 때의 주의사항감정적 민감성 : 연인 간의 성범죄 사건은
+            감정적으로 복잡할 수 있습니다. 피해자와 피고인 모두 개인적인 감정이 크게 얽힐 수 있으며, 이로 인해 사건의 처리 과정에서 심리적 갈등이 발생할 수
+            있습니다. 이를 염두에 두고 사건을 다루는 것이 필요합니다.객관적 증거의 중요성​ : 성범죄 사건에서는 주관적인 진술보다 객관적인 증거가 중요한 역할을
+            합니다. 피해자의 진술, 목격자의 증언, 물리적 증거 등 가능한 한 객관적인 증거를 확보하고 이를 기반으로 사건을 분석하고 대응해야 합니다.법적 공방의 리스크
+            : 연인 간의 성범죄 사건은 법적 공방에서 복잡한 이슈가 제기될 수 있습니다. 예를 들어, 피해자의 동의 여부를 둘러싼 논쟁이나 피해자의 심리적 상태에 대한
+            해석 등이 문제 될 수 있습니다. 이러한 리스크를 미리 예측하고 대응 전략을 준비하는 것이 필요합니다.​(3) 증거 수집 및 법적 대처 방법증거 확보 :
+            성범죄 사건에서는 증거 수집이 중요합니다. 피해자의 신체적 상태를 확인할 수 있는 의료 기록, 사건 발생 당시의 증거, 피해자의 진술 및 목격자의 증언 등이
+            필요 합니다. 증거는 사건의 핵심을 형성하므로, 체계적이고 철저하게 수집해야 합니다.전문가의 의견 활용 : 필요에 따라 정신과 의사, 심리 상담사 등 전문가의
+            의견을 활용할 수 있습니다. 이들은 피해자의 심리 상태나 사건의 정황을 객관적으로 분석하는 데 도움을 줄 수 있습니다.법적 절차에 대한 준비 : 법정에서의
+            대처를 위해, 사건의 진행 절차와 법적 요구사항을 충분히 이해하고 준비해야 합니다. 법원에서의 증거 제출, 진술 준비, 피고인의 방어 전략 등을 철저히
+            준비하는 것이 중요합니다.​​성범죄전문변호사의 조력이 필요한 이유 ​연인 간의 성적 접촉이나 성관계가 상대방의 의사에 반하여 이루어진 경우, 법적으로 성범죄가
+            성립할 수 있습니다. 이로 인해 법적 책임을 지게 될 수 있으며, 이러한 사건은 특히 민감하게 다루어져야 합니다. 법원과 수사기관은 성범죄와 관련된 사건에서
+            피해자의 진술에 중대한 비중을 두고 수사하기 때문에, 정확한 대응이 이루어지지 않을 경우 억울하게 성범죄자로 낙인 찍힐 수 있으며, 사안에 비해 중한 처벌을
+            받을 위험이 있습니다.​연인 간의 성범죄는 그 복잡성과 민감성으로 인해 일반적인 법적 문제와는 다른 접근이 필요합니다. 피해자의 진술이 중요한 증거로 작용하기
+            때문에, 이를 반박하거나 상황을 명확히 설명하기 위해서는 철저한 법적 준비가 요구됩니다. 이러한 준비가 부족하거나 법적 조언 없이 혼자서 대응할 경우, 불리한
+            결과를 초래할 수 있습니다.​따라서, 연인 간의 성범죄로 신고를 당했거나 관련된 법적 문제가 발생한 경우에는 전문적인 법적 조언과 지원이 필수적입니다. 사건
+            초기부터 다양한 성범죄 사건을 경험한 성범죄 전문 변호사의 도움을 받는 것이 매우 중요합니다. 전문 변호사는 사건의 특성을 정확히 분석하고, 법적 전략을
+            수립하여 피해를 최소화하고 권리를 보호하는 데 필요한 모든 지원을 제공합니다. 사건의 초기 단계에서부터 전문적인 법적 도움을 받음으로써, 불필요한 법적
+            리스크를 줄이고 보다 유리한 결과를 도출할 수 있을 것입니다.​결론적으로, 연인 간의 성범죄는 법적, 심리적으로 복잡한 문제를 동반하며, 신속하고 전문적인
+            대응이 필요합니다. 이를 위해 경험이 풍부한 변호사와 함께 사건을 체계적으로 준비하고, 법적 절차를 철저히 이해하며 대응하는 것이 성공적인 사건 해결의
+            핵심입니다.​​</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>assistant</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>7b3ebe32-c284-4c34-bfb5-a4265d5caaf5</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>73eeee22-6582-46e2-9405-c6b60ea28fe8</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>422524a5-d441-4ea3-a941-77859624dcf7</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.451757+09:00</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>[교통사고전문변호사] 음주운전으로 인한 실직, 방어 가능성은?</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[교통사고전문변호사] 음주운전으로 인한 실직, 방어 가능성은?. </t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>prompter</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>73eeee22-6582-46e2-9405-c6b60ea28fe8</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>a0e3b449-50aa-42bd-a97f-b5022a5aa199</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>73eeee22-6582-46e2-9405-c6b60ea28fe8</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>fda2d329-ff84-4c11-bb77-bd7b0176289d</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.451757+09:00</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>들어가며안녕하세요, 저는 수백 건의 음주운전 사건에서
+            무죄, 무혐의, 기소유예, 가벼운 벌금형 등 많은 좋은 결과를 도출해 낸 화성음주운전변호사 이동현변호사입니다.​음주운전으로 인한 실직 문제는 많은 사람들이
+            겪는 심각한 사회적 문제 중 하나입니다. 음주운전은 개인의 생명과 타인의 안전을 위협할 뿐만 아니라, 그로 인해 발생하는 법적 문제와 경제적 어려움도 큽니다.
+            특히 음주운전으로 인해 직장을 잃게 되는 경우, 이는 개인과 그 가족에게 큰 충격과 고통을 안겨줍니다. 이 글에서는 음주운전으로 인해 발생할 수 있는 실직
+            문제를 법적, 사회적 측면에서 살펴보고, 실직을 방어할 수 있는 가능성에 대해 논의하고자 합니다. 이를 통해 음주운전으로 인한 부정적인 결과를 최소화하고,
+            재취업과 사회 복귀를 도울 수 잇는 방법을 모색해 보고자 합니다.​음주운전 처벌?​‘도로교통법’은 ‘누구든지 술에 취한 상태에서 자동차 등을 운전하여서는 아니
+            된다’고 규정하고 있으며, 이를 위반한 경우 혈중알코올농도에 따라 달리 처벌하고 있습니다. ​즉, 도로교통법은 혈중알코올농도가 0.03% 이상 0.08%
+            미만인 경우 1년 이하의 징역이나 500만 원 이하의 벌금에, 0.08% 이상 0.2% 미만인 경우 1년 이상 2년 이하의 징역이나 500만 원 이상
+            1,000만 원 이하의 벌금에, 0.2% 이상인 경우에는 2년 이상 5년 이하의 징역이나 1,000만 원 이상 2,000만 원 이하의 벌금에 처하도록 규정하고
+            있습니다. ​음주운전으로 인한 실직의 사례음주운전으로 인해 실직하는 사례는 여러가지가 있습니다. 일반적으로 다음과 같은 상황에서 실직이 발생할 수
+            있습니다.​직접적인 해고많은 회사들은 음주운전에 대해 무관용 원칙을 적용합니다. 특히 공공기관, 운송업, 경찰, 소방 등 공공안전을 책임지는 직업에서는
+            음주운전 적발 시 즉각 해고되는 경우가 많습니다. 이러한 직업군에서는 음주운전이 직무 수행의 적합성을 크게 저해한다고 판단하기 때문입니다.자격 정지 및 면허
+            취소운전 면허가 필수적인 직업군, 예를 들어 트럭 운전사, 택시 기사, 배달원 등은 음주운전으로 면허가 정지되거나 취소될 경우, 직무를 수행할 수 없게 되어
+            실직으로 이어질 수 있습니다. 이는 생계에 직접적인 영향을 미치게 됩니다.신뢰 상실많은 직장에서 음주운전을 직원의 신뢰도와 연관지어 평가합니다. 특히 금융업,
+            법률업, 교육업 등 높은 도덕성과 신뢰성이 요구되는 직종에서는 음주운전이 회사의 명예와 직결 될 수 있으며, 이는 결과적으로 해고로 이어질 수 있습니다.공공
+            이미지 손상연예인, 운동선수, 정치인 등 공공의 주목을 받는 직업군에서는 음주운전이 대중의 신뢰와 이미지를 크게 손상시킬 수 있습니다. 이러한 경우, 광고
+            계약 해지, 경기 출전 금지 등으로 인해 실직 상황에 놓일 수 있습니다.​음주운전으로 인한 실직은 개인의 생계뿐만 아니라 가족에게도 큰 영향을 미칩니다.
+            따라서 음주운전을 예방하는 것이 무엇보다 중요하지만, 만약 음주운전으로 인해 실직 위기에 처하게 된다면, 법적 보호 장치와 방어 전략을 통해 상황을 최대한
+            긍정적으로 해결할 수 있도록 노력해야 합니다.음주운전으로 인한 실직, 방어 가능성은?​군인 등 공무원의 경우에는 형사처벌 외에도 징계처분을 받을 수 있어
+            주의해야 합니다.​특히, 음주운전의 경우에는 자칫 잘못 대응하는 경우 엄중한 처벌 뿐만 아니라 중한 징계처분이 내려질 수 있어 초기부터 적극적으로 대응해야
+            합니다. ​따라서 형사사건 뿐만 아니라 징계사건에 대해서, 반성문, 탄원서, 정신과 진료 내역서, 음주운전 관련 교육 이수증, 성실한 직장생활을 입증할 수
+            있는 자료 등 여러 자료를 바탕으로, 한순간의 잘못된 판단으로 음주운전을 하게 되었으나 진심으로 반성하고 있다는 점, 다시는 음주운전을 저지르지 않기 위해서
+            정신과 진료를 받고 음주운전 관련 교육을 이수받는 등 최선을 다하고 있다는 점, 성실하게 공직생활을 하였다는 점 등을 적극적으로 어필하며 '이번에
+            한하여 마지막으로 최대한 선처를 내려달라'는 내용의 의견서를 작성하는 것 뿐만 아니라 재판 혹은 징계위원회에 참석해 위 내용에 대해서 적극적으로
+            어필해야 원하는 결과를 얻을 수 있습니다.​그러나 이 모든 것을 혼자서 판단하고 대응하기에 어려움이 있을 수 있으므로 음주운전변호사의 도움을 받는 것이 반드시
+            필요합니다. ​음주운전변호사의 조력이 필요한 이유음주운전은 사회적으로 심각한 문제로 인식되고 있음에도 불구하고, 여전이 '나는 걸리지 않을
+            거야' 혹은 '가까운 거리니 괜찮겠지'라는 안일한 생각으로 음주 후 운전하는 경우가 많습니다. 이런 무책임한 태도는 종종 음주운전
+            적발이라는 심각한 결과를 초래하게 됩니다.​음주운전이 문제로 대두되었을 때, 이를 단순히 경미한 범죄로 여기고 절절한 대응을 하지 않으면, 예기치 않은 엄중한
+            처벌과 큰 불이익에 직면할 수 있습니다. 음주운전으로 인한 법적 처벌 외에도 실직, 사회적 신뢰 상실 등 심각한 후유증을 겪게 될 수 있습니다. 특히 직장
+            내에서의 불이익이나 실직은 개인의 경제적 안정과 가족의 생활에 큰 영향을 미칩니다.​이런 상황에서 가장 중요한 것은 사건 초기부터 화성음주운전변호사
+            이동현변호사의 도움을 받는 것입니다. 음주운전 사건에 대한 충분한 경험과 전문성을 갖춘 화성음주운전변호사 이동현변호사는 법적 대응뿐만 아니라 실직과 같은
+            부수적인 문제에 대한 적절한 조언을 제공할 수 있습니다. 화성음주운전변호사의 도움을 통해 사건의 모든 측면을 체계적으로 대응하고, 법적 절차를 효과적으로
+            처리함으로써 최대한의 보호를 받을 수 있습니다.​결론적으로, 음주운전 문제가 발생했을 때 혼자서 문제를 해결하려 하기보다는, 화성음주운전변호사의 전문적인
+            지원을 받는 것이 바람직합니다. 이는 단순한 법적 조언을 넘어서, 실직 문제 해결과 사회복귀 지원 등 종합적인 대응을 통해 개인의 권리를 보호하고, 장기적인
+            문제 해결을 도울 수 있습니다. 음주운전 예방의 중요성을 인식하고, 문제가 발생했을 때 신속하고 전문적인 대응을 통해 최악의 상황을 피하는 것이 무엇보다
+            중요합니다.​​</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>assistant</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>73eeee22-6582-46e2-9405-c6b60ea28fe8</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>07dcd657-9fe8-4b42-ac8f-564e08b53e50</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>e2f203f4-5f2b-4812-a198-46e487b11c3c</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.451757+09:00</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>공무원 성범죄 연루되었다면?</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">공무원 성범죄 연루되었다면?. </t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>prompter</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>07dcd657-9fe8-4b42-ac8f-564e08b53e50</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1dd7b7b3-a7ea-4829-9b4d-83e1b972ce18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>07dcd657-9fe8-4b42-ac8f-564e08b53e50</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>4b1ca1ac-34f3-4e6a-a302-5b5bd3be60f8</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.451757+09:00</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>공무원 성범죄 연루되﻿었다면?​공무원은 국민을 위한
+            공무를 수행하는 직군으로 국민들에게 어떠한 해가 가해지거나공무원으로서의 품위를 떨어지는 행동에 대해서는 경검찰의 형사 처벌을 넘어 공무원으로서철저히 징계
+            처리가 될 수 있습니다.​특히 공무원 성범죄에 대해서는 더욱 엄중하게 처벌과 징계가 내려지고 있어서어떠한 경우에라도 연루 되지 않는 것이 최선입니다.​하지만
+            본인의 의도가 없었는데도 불구하고 억울하게 연루 되었거나, 실질적인 범법 행위보다 부풀려져과도한 처분이나 징계를 받을 위기라면 어떻게 대처 해야
+            할까요?​통계에 따르면 공무원 성범죄가 연평균 400여명에 달한다고 하는데요이 중에는 경찰청 소속의 공무원이 가장 많았으며 교육부의 공무원들도 비중이
+            높았습니다.​공무원 성범죄 연루상﻿황은?보통 공무원 성범죄 연루된 경우는 강간 또는 강제 추행, 그리고 통신매체 이용 음란죄 등이 많은
+            편이었는데요​공무원이라는 특성상 높은 윤리 기준과 도덕성, 청렴도가 요구 되기 때문에 공무원 성범죄에 연루되었다면 막상 생각 없이 저지른 가벼운 실수 였다고
+            변명한다 할지라도 본인의 앞으로의 삶과 경력에 있어 심각한 결과가 초래 될 수 있습니다.​특히 공무원 성범죄는 형사 처벌에서 최소 처분인 기소유예를 받는다고
+            하더라도 이에 대한 사항이 직속 상부에 보고 되게 되고 품위 유지 의무 위반으로 인해 징계위원회를 거쳐 본인의 공무원에 대한 커리어에 심각한 지장이 초래 될
+            수 있습니다.​공무원 성범죄 종류에 ﻿따른 형량은?성범죄는 피해자의 삶과 정신에 심각한 피해를 초래 하기 때문에 이에 대한 처벌 수위도 높은 편입니다.​강제
+            추행은 협박이나 폭행과 함께 추행을 하는 것으로 10년 이상의 징역, 1500만원 이하의 벌금형에 처해지고,특히 업무상의 관계에 있는 사람, 그 중에서도 보호
+            감독을 해야 할 위치에 있는 사람이 본인의 위계나 위력을 사용하여 추행을 하였다면, 이는 성폭력 처벌법상 업무상 위력등에 의한 추행죄로 가중 처벌 되어 3년
+            이상의 징역이나 1500만원 이하의 벌금에 처해지게 됩니다.​불법촬영은 특히 형량이 높은데요, 카메라등 이용 촬영죄가 적용 되며 7년 이하의 징역이나 5천만원
+            이하의 벌금형에 처해질 수 있으며, 실질적으로 피해자에게 위해를 가한 것 뿐만 아니라 컴퓨터나 휴대폰 등의 통신 매체를 활용하여 성적 수치심이나 혐오감을
+            일으키는 글이나 사진, 영상 등을 보낸 경우에도 통신매체이용 음란 죄로서 2년 이하의 징역이나 2천만원 이하의 벌금형에 처해 질 수 있어 유의 하셔야
+            합니다.​공무원 성범죄, 징계﻿를 피할 수 없기에특히 공무원 성범죄라면 100만원 이상의 벌금형만 받게 되더라 그 형이 확정 되었다면 퇴직사유에 해당하게
+            됩니다.​이러한 경우에는 퇴직을 해야 할 뿐만아니라 퇴직급여나 수당에서도 불이익을 받게 되고, 최소 처분인 기소유예 등의 낮은 처벌을 받게 된다 할지라도
+            감봉이나 파면 등의 징계는 피할 수 없게 됩니다.​기소유예 자체도 처분을 따로 받지 않지만 범죄 사실에 대한 인정이 되는 것이기에 공무원법에 의해 징계를 받게
+            되고 이는 승진이나 승급에 대한 불이익은 물론이고 이러한 상황은 공시생이나 임용예정자에게도 마찬가지로 적용이 됩니다.​때문에 공무원 성범죄에 연루 되신 경우,
+            만약 본인의 무고가 확실한 상태에서 억울한 상황에 처하신 경우라면혹은 잘못은 인정 하지만 과도한 처분이나 징계가 내려진 경우에는 전문적인 법률 조력을 받는
+            것이 매우 중요합니다.​무고를 증명하기 위해﻿선만약 현재 연루 된 공무원 성범죄에 있어서 본인의 무고가 확실 하다면 기소유예 처분 마저 본인에게는 과한 처분이
+            될 수 있기에 완전 무결하게 무고를 증명 하기 위해 소청 심사청구나 헌법소원까지도 고려 하셔야 합니다.​특히 소청 심사청구를 하려면 처분이 있는 것을 안 날로
+            부터 30일 이내에 청구서를 제출 하셔야 하고 반드시 전문 법률 전문가와의 조력을 통해 본인에게 유리한 방향으로 진행 할 수 있도록 대처 하셔야
+            하겠습니다.​성범죄사건﻿의 형벌이 높기에성범죄 사건은 형벌 수위가 높고 법적 절차가 매우 복잡하고 까다롭습니다​증거 수집, 증언, 법률 해석 등 모든 과정이
+            정교하게 이루어져야 하며, 이를 잘못 처리할 경우 불리한 결과를 초래하여 본인의 공무원으로서의 앞으로의 커리어 등에도 심각한 영향을 줄 수 있어 반드시 전문
+            변호사를 통해 체계적인 플랜으로 접근 하여 해결 할 수 있도록 방법을 찾으셔야 합니다.​공무원이 성범죄에 연루된 경우형사처벌 뿐 아니라 특수한 신분에 따른
+            앞으로의 장래에도 큰 영향을 주게 됩니다.때문에 믿을만한 전문 변호사의 조력은 필수 입니다.​변호사 선임의 중﻿요성법적 절차의 복잡성과 방어 전략 수립,
+            증거의 수집과 활용에 대한 전문성을 갖춘 저희 법무법인 대한중앙의전문 변호사와 함께 공무원 성범죄에 연루된 상황에서 절대 혼자서 해결하려 하지 마시고전문적이고
+            체계적인 도움을 받으시기 바랍니다.​저희 법무법인 대한중앙은 의뢰인의 최선의 이익을 위해 곁에서 최선을 다해 돕겠습니다.언제든 상담 문의 주시기 바랍니다#
+            공무원 소청 변호사, 공무원 징계 변호사, 공무원 성범죄, 수원성범죄전문변호사</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>assistant</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>07dcd657-9fe8-4b42-ac8f-564e08b53e50</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>b3d4b7ca-a8b1-4dc1-ba38-641a8208dd42</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>986bd313-36de-4427-9386-2702d67114f2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.451757+09:00</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>아동학대 관련 범죄로 취업제한명령을 받게 된다면 -아동학대변호사</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아동학대 관련 범죄로 취업제한명령을 받게 된다면 -아동학대변호사. </t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>prompter</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>b3d4b7ca-a8b1-4dc1-ba38-641a8208dd42</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>22260dcd-e53a-4931-9537-10e36f4728e8</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>b3d4b7ca-a8b1-4dc1-ba38-641a8208dd42</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>c11f8f7e-7383-4e77-91b3-6928a7e5ee1e</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.452754+09:00</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>아동학대 관련 범죄로 취﻿업제한명령을
+            받게된다면?​안녕하세요. 법무법인대한중앙 아동학대 전문 변호사 조기현입니다.아동교육, 보육기관 등에 종사하시는 분들이 아동학대에 연루된다면 취업제한에 대한
+            고민도 따르게 됩니다.예를 들어, 교사가 취업제한 명령을 선고 받는 경우, 파면이나 해임과 같은 징계를 받지 않더라도 더이상 학교에 근무할 수 없게 되며,
+            어떤 경우에는 직에서 물러나야 할 수도 있기 때문이죠.​따라서 아동학대 관련 범죄로 기소가 되면 취업제한명령의 유무도 매우 중요합니다.오늘은 구체적인 사례를
+            통해 취업제한 명령 대상자에 포함되는 경우에 대해 알아보겠습니다.아동학대범죄자 취업제한제도﻿란?​아동학대 취업제한 제도란 아동학대 관련범죄로 형 또는
+            치료감호를 선고받아 확정된 사람에게 형 또는 치료감호의 전부 또는 일부의 집행을 종료하거나 집행이 유예, 면제된 날부터 일정기간 동안 아동관련 기관을
+            운영하거나 아동관련 기관에 취업 또는 사실상 노무를 제공할 수 없도록 한 것을 말합니다. 형 또는 치료감호 선고를 받는 사람이라면 취업제한 대상자가 되기
+            때문에 아동학대 관련 범죄로 실형이 나오지 않더라도 (경미한 아동학대 범죄로 벌금형, 집행유예를 받았다 하더라도) 취업제한이 가해질 수 있습니다.
+            취업제한명령은 아동학대 관련범죄 사건의 판결과 동시에 선고(약식명령의 경우에는 고지)되며, 취업제한 기간은 10년을 초과할 수 없습니다.​아동복﻿지법
+            제29조의3 (아동관련기관의 취업제한 등)​① 법원은 아동학대관련범죄로 형 또는 치료감호를 선고하는 경우에는 판결(약식명령을 포함한다. 이하
+            같다)로 그 형 또는 치료감호의 전부 또는 일부의 집행을 종료하거나 집행이 유예ㆍ면제된 날(벌금형을 선고받은 경우에는 그 형이 확정된 날을 말한다)부터
+            일정기간(이하 "취업제한기간"이라 한다) 동안 다음 각 호에 따른 시설 또는 기관(이하 "아동관련기관"이라 한다)을
+            운영하거나 아동관련기관에 취업 또는 사실상 노무를 제공할 수 없도록 하는 명령(이하 "취업제한명령"이라 한다)을 아동학대관련범죄 사건의
+            판결과 동시에 선고(약식명령의 경우에는 고지를 말한다)하여야 한다. 다만, 재범의 위험성이 현저히 낮은 경우나 그 밖에 취업을 제한하여서는 아니 되는 특별한
+            사정이 있다고 판단하는 경우에는 그러하지 아니하다.​​다만 아동학대 관련 범죄를 저지른 사람에게 반드시 취업제한 명령이 내려지는 것은 아닙니다. 재범의
+            위험성이 현저히 낮은 경우나, 아동학대 행위가 지속적이지 않은 우발적인 행위라면 취업제한 명령이 면제될 수 있습니다. 따라서 법원은 당사자의 재범위험성 등을
+            판단하기 위해 취업제한 명령을 선고하기 전에 정신건강의학과 의사, 심리학자, 사회복지학자, 아동학대 관련 전문가, 그 밖의 관련 전문가로부터 취업제한 명령
+            대상자의 재범 위험성 등에 관한 의견을 들을 수 있도록 하고 있습니다. 취업제한에 해﻿당하는 기관은? ​취업제한에 해당하는 기관은 아래와 같습니다. 1.
+            보장원, 취약계층 아동 통합서비스 수행기관, 아동보호 전문기관, 다함께돌봄센터, 가정위탁지원센터, 아동복지시설2. 긴급전화센터, 가정폭력 관련 상담소,
+            가정폭력 피해자 보호시설3. 건강가정 지원센터4. 다문화 가족지원센터5. 성매매 피해자 등을 위한 지원시설 및 성매매 피해 상담소6. 성폭력 피해 상담소 및
+            성폭력 피해자 보호시설 및 성폭력 피해자 통합지원센터7. 어린이집, 육아종합지원센터, 시간제 보육서비스 지정기관8. 유치원9. 의료기관(의료인에
+            한정한다)10. 장애인복지시설11. 정신건강복지센터, 정신건강증진시설, 정신요양 시설 및 정신재활시설12. 공동주택의 관리사무소(경비업무 종사자에
+            한정한다)13. 청소년시설, 청소년단체14. 청소년활동시설15. 청소년 상담복지센터, 이주배경청소년지원센터 및 청소년쉼터, 청소년 자립지원관, 청소년
+            치료재활센터16. 청소년 보호ㆍ재활센터17. 체육시설 중 아동의 이용이 제한되지 아니하는 체육시설로서 문화체육관광부 장관이 지정하는 체육시설18. 학교 및
+            학습부진아 등에 대한 교육을 실시하는 기관19. 학원 및 교습소 중 아동의 이용이 제한되지 아니하는 학원과 교습소로서 교육부 장관이 지정하는 학원ㆍ교습소20.
+            한 부모가족복지시설21. 아동보호 전문기관 또는 학대 피해 아동 쉼터를 운영하는 법인22. 소년원 및 소년분류심사원23. 아동인권, 아동복지 등 아동을 위한
+            사업을 수행하는 비영리법인(대표자 및 아동을 직접 대면하는 업무에 종사하는 사람에 한정한다)24. 아이돌봄서비스 제공 기관 취업제한 명령이 ﻿내려진
+            사례​CASE 1. 어린이집의 담당 교사 A씨는 피해아동에게 미술활동에 참여 할 것을 권유하였으나 아동이 이를 거부하였다고 합니다. 그리고 A씨는 이를 이유로
+            아이를 구석으로 데리고 간 다음 팔과 다리를 붙잡고 움직이지 못하게 한 뒤, 손으로 피해아동의 다리를 2회 때리고, 계속하여 피해아동을 안고 자리에서 일어난
+            다음 손으로 피해아동의 등을 2회 때리고, 손으로 피해아동의 등을 부여잡았다고 합니다. 본 행위에 대해 법원은 징역 4월의 2년간 집행유예, 2년간 취업제한이
+            선고하였습니다. CASE 2. 어린이집 보육교사 B씨는 피해아동의 담당교사였다고 합니다. 피해아동은 사건 당일 낮잠 시간에 자지 않고 일어나 옆에서 잠을 자고
+            있는 다른 아동의 몸을 흔들어 깨웠다고 합니다. B씨는 이를 이유로 손으로 아동의 어깨 부위를 1회 밀치고 옆구리 부위를 3회 밀치고, 머리 부위를 1회 세게
+            밀친 후, 피해자의 앞에 앉아 손으로 피해자의 옆구리를 4회 찔렀다고 합니다. 재판부는 본 사건에 대해 징역 6월의 2년간 집행유예, 3년간의 취업제한을
+            선고하였습니다. CASE 3. 피고인 C씨는 어린이집 보육교사로 근무 중 과실로 아동에게 약 5주간의 치료가 필요한 2도 화상을 입힌 바가 있었으며 수개월
+            동안 만0세~만1세에 불과한 피해아동들을 상대로 30차례 이상 지속적으로 정신적·신체적 학대를 하였습니다. 1심 재판부에서는 C씨에게 징역 8월, 3년간의
+            취업제한을 선고하였으나 2심에서 합의를 한 점이 고려되어 징역8월의 2년간 집행유예, 3년간의 취업제한을 선고하였습니다.​​ 아동학대 취업제한 명령에 ﻿어떻게
+            불복할 수 있나요? 아동학대로 형 또는 치료감호와 함께 취업제한 명령을 선고받고 확정되지 않았다면, 항소를 하여 무죄판결을 받거나 선고유예 판결을 받아
+            취업제한 명령을 받지 않을 수 있습니다. ​또한 취업 제한 기간이나 취업제한 명령이 현저히 부당하거나, 취업을 제한하여서는 아니 되는 특별한 사정이 있는
+            경우에는 취업제한 기간의 변경 또는 취업제한의 면제를 취업제한 결정을 고지 받은 7일 이내에 항고할 수 있습니다. 이때의 항고가 기각될 시에는 7일 이내에
+            재항고를 할 수 있으며, 재항고의 경우에는 위 결정이 법령에 위반된 경우일 때만 가능합니다.# 아동학대변호사, 아동학대전문변호사, 어린이집전문변호사, 아동학대
+            취업제한, 보육교사 아동학대, 유치원 아동학대</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>assistant</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>b3d4b7ca-a8b1-4dc1-ba38-641a8208dd42</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>a807b1d6-92a6-416f-9147-c8c59ed6ff7f</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>b3913b59-ad3c-431d-95a6-3de782045480</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.452754+09:00</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>성범죄, 강제추행, 클럽에서 원나잇 후 인생 X</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">성범죄, 강제추행, 클럽에서 원나잇 후 인생 X. </t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>prompter</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>a807b1d6-92a6-416f-9147-c8c59ed6ff7f</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>a84ec115-9e88-4acd-8328-2e97c25c99b3</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>a807b1d6-92a6-416f-9147-c8c59ed6ff7f</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>6b158a68-0229-458c-a83c-7279d7ffdd0c</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.452754+09:00</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>준강간.. 준강제추행.. 나하고는 전혀 상관없는
+            범죄다! 라고 생각하실 텐데요. 그런데 실제로 이러한 범죄로 상담 오시는 분들은 놀랍게도 대부분 그냥 평범한 분들이세요. 사실 이런 범죄는 피해자랑 합의가 안
+            되면 실형을 받는다고 생각해야 할 정도로 중범죄거든요? 합의가 되더라도 한두 푼이 아니라 수천만 원이 들기도 하고요. 그렇다면 어째서 이런 중범죄를 평범한
+            일반인들이 저지르게 되는 걸까요?   여러 가지 이유가 있을 수 있겠지만 그중 하나는 바로 ‘원나잇’ 때문인데요.아니, 원나잇이 왜? 라고
+            하시는 분들 분명히 계실거예요~ 하지만 오늘부터는 생각이 달라질 수 있으니깐 끝까지 함께 해 주시기 바랍니다!   그럼 먼저 ‘준강간,
+            준강제추행’이 뭘까요? 먼저 강간이나 강제추행은 사람을 폭행 또는 협박해서 ‘강제로’ 성관계나 스킨십을 하는 경우인데요 그럼 술에 만취한 사람의 경우라면
+            어떨까요? 이 사람을 강간하기 위해서 굳이 폭행이나 협박이 필요할까요? 필요없겠죠 이런 사람을 상대로 성행위나 스킨십을 한다면, 이건 상대방의
+            동의를 받지 않고 ‘강제로’ 하는 거나 다름 없다는 거예요. 쉽게 말해서 강간이나 강제추행과 마찬가지로 보겠다, 라는 거죠.   그럼 다시
+            원나잇 이야기로 돌아와서 제가 실제 진행했던 사건을 가지고 원나잇의 위험성에 대해 이야기를 해 볼께요.A라는 남성이 친구들과 클럽에 갔어요. 한참 술을
+            마시면서 놀다가 다른 여성분들과 합석을 했는데, 그 중 B라는 여성과 서로 마음이 통해서 따로 나왔고 모텔 가서 원나잇을 한 거죠. A남의 입장에서는 나도
+            취했고, 상대방도 취하긴 했지만 어쨌든 서로 뜻이 통했다고 생각한거죠. 심지어 모텔에서 성관계를 하는 동안에도 아무 문제가 없었으니 말 그대로 원나잇으로
+            끝났다고 생각하고 잘 지내고 있었는데요.그런데? 어느 날 갑자기 경찰서에서 준강간 가해자로 고소당했으니 조사 받으러 오라고 연락을 받은거죠. 왜 이런 일이
+            일어난 걸까요?   물론 B녀가 처음부터 합의금을 노린 꽃뱀일 수도 있겠죠. 그런데 다 그렇진 않고. B녀 입장에서도 분명히 할 말이 있는
+            거예요.클럽에서 친구들과 함께 놀다가 어떤 남성들이랑 합석하고 어렴풋이 A남이랑 따로 이야기를 나눈 것까지도 생각이 나는데, 그 이후론 블랙아웃~ 필름이 끊긴
+            거죠. 그러고 눈을 떠 보니? 다음 날 모텔 침대에 낯선 남자랑 같이 있는 거예요. B녀 입장에서는 아무 기억이 안 나니까 일단 ‘당했다!’라고 생각하고
+            경찰서에 고소부터 하는 거죠,   여기서 제가 말씀드리고 싶은 건 A 남과 같이 갑자기 고소를 당했을 때의 대처방법인데요  
+            먼저, 앞 뒤 안 가리고 무조건 사과부터 한다?! 이거 절대 안됩니다!!! 물론 이런 상황에 처하게 되면 누구나 당황을 하겠죠. 그래서 일단 “어제일은 내가
+            잘못했다”라고 무조건 사과부터 하는 분들이 참 많은데요. 이건 그냥 내가 성범죄를 인정하는 것이기 때문에 이와 같은 행동은 절대 하면 안
+            되고요 일단은 그 여성분과 어제 일은 서로 합의하에 이루어진 성관계다 라는 점을 명확하게 하시라는 거죠   즉, 여성분이 문자나 전화로
+            남성분에게 “내가 만취해서 기억이 없을 때 너가 강제로 나를 강간한거 아니냐”라고 일방적으로 추궁할 때 무조건 미안하다 가 아니라 나는 너와 강제로 성관계를
+            한 것도 아니고 내 입장에서는 그 당시 니가 성관계에 동의한다고 생각할 수밖에 없는 상황있었다, 라는 점을 상세하게 설명하는 게 필요하다라는 겁니다.
+              또한 여기서 범죄 혐의를 벗을 수 있는 중요 포인트는 ‘상대방이 만취상태가 아니었다’는 사실을 주장, 입증하는 건데요. 상대방은 술에
+            만취한 상태에서 억지로 모텔로 끌려갔고 강제로 성관계가 이루어졌다고 주장하고 있는 상황이잖아요. 따라서 술을 마시긴 했지만 만취상태는 전혀
+            아니었다, 스스로 원해서 함께 모텔로 이동했고 합의하에 성관계를 한 것이지 강제성은 없었다, 라는 점을 입증할 수 있는 자료 확보가 중요하다고 할 것입니다.
+              예를 들면 술집이나 모텔, 또는 모텔 앞 편의점이나 가게에서의 모습이 담긴 CCTV나 결제내역 같은 것들.. 만일 CCTV에서의 모습이
+            연인같이 다정하고, 상대방도 멀쩡하게 잘 걷고, 심지어 적극적으로 팔짱을 낀다거나 스킨십을 하고 있더라~ 이건 유리한 자료가 되겠죠. 특히 모텔에서 결제를
+            여성분이 한 경우에는 이것 또한 매우 유리한 사정이 될 수 있구요.     제가 직접 진행한 사건 중에서도 여성분이 만취
+            상태로 아무 기억이 없다며 남성분을 준강간으로 고소했던 케이스가 있었는데요. 나중에 보니 남성분이 모텔에서 씻는 동안 기다리면서 자신의 지인과 정상적으로
+            통화도 하고, 카톡도 하고 했던 기록들이 확인된 경우가 있었구요. 심지어는 성관계 이후 다음 날 아침에 함께 밥을 먹고 집까지 데려다 줬고,그 후로도 약
+            3개월 정도 카톡으로 호감 있는 대화를 계속 나누었는데 갑자기 고소가 이루어진 사건도 있었습니다. 모두 무혐의로 잘 끝난 사건이었지만
+            당사자들은 사건이 끝날때까지 마음 고생이 심하셨죠.   따라서 오늘의 결론은 뭐다? 원나잇은 원나잇으로 끝나지 않을 수도 있다! 성범죄로
+            고소될 가능성이 충분히 있다는 것, 꼭 명심하시구요~</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>assistant</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>a807b1d6-92a6-416f-9147-c8c59ed6ff7f</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>21f3a947-60b8-4d7f-872b-e22619cbc988</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>68e9e090-a0ad-4733-835d-472ade84d923</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.452754+09:00</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>트럼프를 저격한 사람과 사냥중 실수로 사람을 쏜 사람은 똑같이 처벌받을까?</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">트럼프를 저격한 사람과 사냥중 실수로 사람을 쏜 사람은 똑같이 처벌받을까?. </t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>prompter</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>21f3a947-60b8-4d7f-872b-e22619cbc988</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>5c5cdb94-98be-4926-b963-faa60c58ccc9</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>21f3a947-60b8-4d7f-872b-e22619cbc988</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>fa908606-7818-4b4d-9df5-5b172b36d822</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.452754+09:00</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Focus ON - 트럼프를 저격한 사람과 사냥중
+            실수로 사람을 쏜 사람은 똑같이 처벌받을까?이미지 출처 : 셔터스톡 / 편집 : 시끌법적팀대통령 후보를 저격했다면?애초부터 특수한 목적성을 가지고, 즉 시해를
+            목적으로 행동했다고 볼 수 있습니다. 총은 대표적인 살상무기이니 살인미수죄가 적용될 수 있겠죠. 더군다나 대통령 후보에 대한 범죄는 사회적 이목을 끄는 중대한
+            사건으로서 특별사법경찰관리의 수사 개시 보고 대상이 됩니다. 또한 대통령 후보를 피격하는 행위는 선거의 자유를 침해하는 중대한 공직선거법 위반에 해당합니다.
+            공직선거법 제246조에 따르면 다수인이 집합하여 투표소 등에서 폭행, 협박 등으로 선거의 자유를 방해한 주모자는 3년 이상의 유기징역에 처하도록 하고
+            있습니다.공직선거법 제246조(다수인의 선거방해죄)① 다수인이 집합하여 제243조(投票函 등에 관한 罪) 내지 제245조(投票所 등에서의 武器携帶罪)에 규정된
+            행위를 한 때에는 다음 각호의 구분에 따라 처벌한다.1. 주모자는 3년 이상의 유기징역2. 다른 사람을 지휘하거나 다른 사람에 앞장서서 행동한 자는 2년 이상
+            10년 이하의 징역3. 부화하여 행동한 자는 5년 이하의 징역② 제243조 내지 제245조에 규정된 행위를 할 목적으로 집합한 다수인이 관계공무원으로부터 3회
+            이상의 해산명령을 받았음에도 불구하고 해산하지 아니한 때에는 그 주도적 행위자는 5년 이하의 징역에 처하고, 기타의 자는 1년 이하의 징역 또는 200만원
+            이하의 벌금에 처한다.우리나라에서도 정치인들을 대상으로 한 피격, 피습 사건은 꾸준히 발생하였는데, 올초에 발생한 이재명 더불어민주당 대표의 사건의 범인에게는
+            살인 미수와 공직선거법 위반등의 혐의로 징역 15년의 중형이 선고되기도 했습니다.유사한 미국의 사례를 살펴보면, 존F 케네디 전 미국 대통령의 동생인 로버트
+            케네디 전 상원의원이 대선에 출마하였으나 1968년 6월 캘리포니아 주 예비선거에서 승리한 뒤 총격을 받고 사망한 사건이 있었습니다. 암살범인 시르한은
+            50여년이 넘도록 수감중입니다.사냥 중 실수로 사람을 쐈다면?우리나라에서는 [총포ㆍ도검ㆍ화약류 등의 안전관리에 관한 법률]에 따라 허가를 받아 제한적으로
+            총기를 소지 할 수 있습니다. 총기 소지와 관련된 상세한 내용은 총포화약안전관리시스템에서 확인할 수 있습니다.야생생물 보호 및 관리에 관한 법률에 의하면,
+            수렵장에서 수렵동물을 수렵하는 사람은 수렵면허를 받아야 합니다.야생생물 보호 및 관리에 관한 법률 제44조(수렵면허)① 수렵장에서 수렵동물을 수렵하려는 사람은
+            대통령령으로 정하는 바에 따라 그 주소지를 관할하는 시장ㆍ군수ㆍ구청장으로부터 수렵면허를 받아야 한다.② 수렵면허의 종류는 다음 각 호와 같다.1. 제1종
+            수렵면허: 총기를 사용하는 수렵2. 제2종 수렵면허: 총기 외의 수렵 도구를 사용하는 수렵③ 제1항에 따라 수렵면허를 받은 사람은 환경부령으로 정하는 바에
+            따라 5년마다 수렵면허를 갱신하여야 한다.④ 제1항에 따라 수렵면허를 받거나 제3항에 따라 수렵면허를 갱신하려는 사람 또는 제48조제3항에 따라 수렵면허를
+            재발급받으려는 사람은 환경부령으로 정하는 바에 따라 수수료를 내야 한다.[전문개정 2011.7.28]유해조수 구제 활동의 일환으로 농가등에서 멧돼지를 사냥하는
+            사례가 있는데, 이 과정에서 총기 사고가 발생하는 경우가 있습니다. 앞서 이야기한 로톡의 상담사례도 동료 엽사를 멧돼지로 오인해 총기를 발포하여 발생한
+            사고입니다. 이와 같은 경우는 애초부터 사람에게 쏘기 위한 목적으로 발포한게 아니다보니 ‘살인미수죄’ 보다는 ‘업무상 과실치상’의 혐의가 적용되는 경우가
+            많습니다. 판례를 통해 확인해보겠습니다.총기 관련 사건에서 과실치상으로 인정된 판례</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>assistant</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>21f3a947-60b8-4d7f-872b-e22619cbc988</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>f3a86f0b-4d1d-49a4-83d4-918c91a93d6b</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>4915c19e-f73a-4348-bd92-a50976ae2b46</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.452754+09:00</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>편의점 점주 vs</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">편의점 점주 vs. 편의점 알바생. </t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>prompter</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>f3a86f0b-4d1d-49a4-83d4-918c91a93d6b</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>0d953bcb-3da5-45f9-8095-cf053bb09ba0</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>f3a86f0b-4d1d-49a4-83d4-918c91a93d6b</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>8b145cd2-c98e-4953-8e65-1f7fe0db42bb</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.452754+09:00</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>5900원짜리 족발 세트 폐기 찍고 먹었다고 알바생
+            고소한 편의점 점주...결말은? (w.시끌법적)이미지 출처 : 시끌법적 영상 캡처편의점 알바생이 점주에게 고소를 당했습니다.5,900 원 짜리 반반족발세트를
+            일부러 폐기처리 하고 먹었다는 건데요.근무 6일 차에 횡령죄로 고소된 알바 A씨.사실A씨가 상품판매 시간이 아직 남았는데도 족발을 폐기하고 먹긴
+            했습니다.그렇다면 이게 실수 인지 고의 인지 봐야 하는데요.횡령 째는 '고의성이 입증돼야만 처벌할 수 있는 범죄이기 때문입니다.제355조(횡령,
+            배임)① 타인의 재물을 보관하는 자가 그 재물을 횡령하거나 그 반환을 거부한 때에는 5년 이하의 징역 또는 1천500만원 이하의 벌금에 처한다. [개정
+            1995. 12. 29.]② 타인의 사무를 처리하는 자가 그 임무에 위배하는 행위로써 재산상의 이익을 취득하거나 제삼자로 하여금 이를 취득하게 하여 본인에게
+            손해를 가한 때에도 전항의 형과 같다.이미지 출처 : 시끌법적 영상 캡처편의점에서는 상품별로 폐기하는 시간이 다릅니다.도시락, 햄버거,샌드위치는 보통 저녁
+            7:30김밥,빵, 유제품, 그리고 '냉장식품'은 저녁 11시 반에 폐기하는데요.A씨가 먹은 족발은 냉장식품이지만 포장상태는 편의점도시락과 유사한
+            모양이었죠.이미지 출처 : 시끌법적 영상 캡처그래서 이 사건의 판사는 "A씨가 충분히 혼동할 수 있었다"고 판단해 무죄를 선고했습니다.또
+            점주가 사전에 도시락과 냉장식품의 종류에 대해 교육한 적이 없었기 때문에 알바 6일 차였던 A씨가 착각할 수 있었다고 봤죠.게다가 A씨가 이 편의점에서
+            근무하는 5일 동안 최소 15만원 이상의 사비를 들여 상품을 산 것도 무죄의 이유였는데요.만약 A씨가 족발을 먹고싶었다면 횡령이 아니라 본인 돈으로 구매 했을
+            거라고 판단했습니다.&amp;gt;&amp;gt; 시끌법적 유튜브에서 확인하기로톡에서 찾아본 편의점 폐기 관련 분쟁로톡 상담사례(1) - 편의점
+            폐기음식 제공을 구두로 허락받았으나 근무시간에 친구에게 폐기를 주어 해고당한 사례</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>assistant</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>f3a86f0b-4d1d-49a4-83d4-918c91a93d6b</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20888933-077c-4d8c-af73-e73fb55da303</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>9ff60440-f22a-4efe-aed6-bc01452fe4ed</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.452754+09:00</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>유부남 아이를 가진 뒤 상간소 피고가 된 경우 예상되는 법적문제</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">유부남 아이를 가진 뒤 상간소 피고가 된 경우 예상되는 법적문제. </t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>prompter</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>20888933-077c-4d8c-af73-e73fb55da303</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2092550a-923b-4c94-862f-5cc13f310067</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>20888933-077c-4d8c-af73-e73fb55da303</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ffd6bbba-b443-4486-92b6-601df0d36392</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.452754+09:00</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>돌싱이란 돌아온 싱글의 준말로, 이혼남, 이혼녀를
+            다르게 부르는 말입니다. ​여성가족부가 발표한 '2022 통계로 보는 남녀의 삶'에 따르면 2021년 결혼한 신혼부부 중 여성과 남성 모두
+            재혼이거나 둘 중 한 명이 재혼을 한 경우는 전체의 22.2%로 새로 결혼하는 커플 다섯 명 중 한 명은 돌싱으로 나타났습니다.​증가하는 이혼율만큼이나 재혼율
+            역시 증가하는 것을 알 수 있는데요,​또 한 편으로는 이제 '돌싱'은 배우자의 선택기준에서 더이상 장애가 되지 않는다는 방증이기도
+            합니다.​그런데 돌싱이라는 말만 믿고 교제를 해오다 아이를 가졌는데, 뒤늦게 상대가 유부남, 즉 이혼상태가 아니라는 사실을 알게 되었다면 상황이 참으로
+            복잡해집니다.​우선 아이의 출생신고가 난감해지고, 본인은 상간소 피고가 될 수 있으며, 중혼적 사실혼 관계가 되어 법적 보호도 받기 어려워지기
+            때문입니다.​이번 시간에는 유부남이라는 사실을 속인 돌싱과 교제하다가 아이가 생긴 경우, 각종 야기될 수 있는 법적 문제와 그 해결법에 대해 알아보도록
+            하겠습니다.﻿﻿유부남의 아이를 가진 경우 아이의 출생신고는?﻿﻿ 기본적으로 법률상 부부 사이에서 아이가 출생하면, 부부 중 누가 출생신고를 하더라도 부부의
+            자녀로 가족관계등록부상에 기재됩니다.​그런데 혼인하지 않은 상태에서 아이를 출산하게 되면, 생물학적 친부가 인지신고를 해야 친부의 가족관계등록부 상에 법적
+            자녀로 올라갑니다. ​친부가 인지를 거부하면 '모'는 친부를 상대로 인지청구소송을 통해 자신의 아이를 친부의 호적에 올릴 수 있습니다.
+            ​유부남의 아이를 출산하여 출생신고를 하려는 경우에도 혼외자녀를 친부의 호적에 올리려한다면 친부가 인지신고를 하거나, 인지신고를 거부할 경우 소송을 통해
+            해결할 수 있습니다.​만일 '모'가 친부의 호적에 올라가는 것을 거부한다면 '모' 스스로 출생신고를 하여 자신의 호적에
+            '모'의 성(姓)으로 자녀를 올릴 수도 있습니다.​다만 이 경우 법률상 '친부'의 존재는 자녀의 가족관계등록부에 표기되지
+            않습니다.﻿유부남과 외도 상간소 피소 가능성과 대응﻿돌싱인 줄 알고 만났는데, 결과적으로 상대방이 이혼하지 않는 상태임을 알았다면 상대배우자로부터
+            상간자위자료청구소송을 당할 수 있습니다.​이 경우 상간이 아님을 입증해야 위자료 책임을 면할 수 있는데요, ​이를 위해서는 교제남이 자신을 돌싱이라고 속인
+            사실을 입증해야 합니다. ​상간자위자료책임은 상간자가 교제상대가 기혼자임을 알고도 만나는 경우에만 불법행위에 해당해 손해배상책임을 지기 때문입니다.​만일
+            돌싱이라고 속인 사실이 입증된다면 역으로 유부남을 상대로 성적자기결정권침해에 따른 위자료를 청구할 수 있고, 결혼을 미끼로 교제남성이 금전을 요구해서
+            갈취했다면 혼인빙자사기죄로 형사처벌을 구할 수도 있습니다.﻿돌싱이라고 속인 유부남과 사실혼 관계에 있는 경우 중혼적 사실혼 상태의 법적 문제﻿ 이미 법적으로
+            배우자가 있는 사람과 동거하면서 형성한 사실혼 관계를 '중혼적 사실혼'이라고 하는데, 중혼적 사실혼은 보통의 사실혼과는 달리 원칙적으로 법의
+            보호를 받지 못합니다. ​대법원은 기본적으로 “법률상 혼인을 한 부부가 별거하고 있는 상태에서 그 다른 한쪽이 제3자와 혼인의 의사로 실질적인 부부생활을 하고
+            있다고 하더라도, 특별한 사정이 없는 한 이를 사실혼으로 인정하여 법률혼에 준하는 보호를 할 수는 없다"라는 입장입니다.(대법원 2010. 3.
+            25. 선고 2009다 84141 판결)​그러나, 만일 상대방의 법률상 혼인관계가 이혼으로 종료되거나 ‘사실상 이혼 상태’와 다름없다면 예외적으로 보호받을 수
+            있습니다. ​예를 들어 전 배우자와의 연락 두절로 사실상 이혼 상태에 이른 뒤, 또 다른 배우자와 혼인관계를 유지하는 경우에는 이전 혼인관계가 사실상 이혼
+            상태였음을 입증하는 것으로 사실혼 관계로도 법적 보호를 받을 수 있습니다. ​기존 혼인관계가 사실상 이혼 상태였음을 법적인 판단을 통해 인정받게 된다면 중혼적
+            사실혼 배우자는 일반 사실혼에 준하는 법적 보호와 권리를 행사할 수 있는데, 예를 들어 상대방이 사망하거나 사실혼 관계가 종료했을 때 상대방의 보험금·연금을
+            타거나 재산분할청구권 행사가 가능합니다.법률사무소 카라 유지은 대표변호사는 이혼/상속전문변호사로 직접 상담합니다.</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>assistant</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>20888933-077c-4d8c-af73-e73fb55da303</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>38107df5-aaf8-401c-8f4f-f9bb1d7fc9e9</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>fdf9d3cc-4401-456e-81c5-2d219f63ae3b</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.453754+09:00</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>소송 후 반환 받는 변호사 보수의 범위</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">소송 후 반환 받는 변호사 보수의 범위. </t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>prompter</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>38107df5-aaf8-401c-8f4f-f9bb1d7fc9e9</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>384be157-e8a1-44bc-8c41-31543b0286e4</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>38107df5-aaf8-401c-8f4f-f9bb1d7fc9e9</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>dccaf72a-db37-478a-a786-a160465b068f</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.453754+09:00</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>소송을 꼭 해야 하는 시점이 인생에 한번쯤 있기
+            마련입니다.​상담을 하다보면 의뢰인 분들께서 항상 변호사 비용을 상대방에게 청구할 수 있는지 물어보시는 분들이 많습니다.​소송 하면서 내 시간 쓰는 것도
+            억울한데 변호사 비용까지 부담하면 억울한 심정이라 그러실텐데요.​답변 먼저 드리면, 전부 승소하더라도 규정 상 소송가액에 비례하여 받을 수 있는 금액만 받을
+            수 있습니다.​순서대로 살펴보겠습니다.먼저 판결문에는 주가 되는 금액 외에, 소송비용에 대한 주문이 포함되어 있습니다. ​소송비용은 법원에 내는 인지송달료와
+            변호사 보수를 합한 개념입니다​예를 들면요, 전부 승소의 경우에는 피고에게 모든 소송비용을 부담시킵니다.​소송비용은 피고가 부담한다일부 승소의 경우에는
+            피고에게 청구금액 대비 인용금액 비율에 따른 소송비용 분담 주문이 기재됩니다.소송비용 중 40%는 원고가, 60%는 피고가 각 부담한다.따라서 청구금액 대비
+            승소금액의 비율에 따라 소송비용 분담비율이 정해지게 됩니다. 대법원 규칙인 변호사보수의 소송비용 산입에 관한 규칙에는 변호사 보수의 산정 기준에 대해 정해두고
+            있습니다.위 도표의 산식에 따라 변호사 보수를 계산하게 됩니다. ​예를 들면 소송가액이 2,000만원이면 200만원이겠고요, 5000만원이면
+            440만원이겠습니다.​여기에 앞서 알아낸 소송비용 분담비율을 곱하면 내가 상대방에게 받을 수 있는 변호사 보수가 나오게 됩니다.​따라서, 아래와 같이
+            기억하시면 됩니다.상대방으로부터 받을 수 있는 변호사 보수 = 대법원 규칙에 따른 변호사 보수액 X 소송비용 분담비율﻿위에서 결정된 금액을 토대로, 판결이
+            확정되면 1심 법원에 소송비용 확정결정신청을 해서 받는 순서입니다.길고 긴 소송절차에 비용까지 걱정이 많으실텐데요, 그래도 전부 승소의 경우 지출하신 변호사
+            비용을 상당부분 보전받을 수 있는 길이 있습니다. 주저하지 말고 권리를 찾기 위한 용기를 내셨으면 합니다.</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>assistant</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>38107df5-aaf8-401c-8f4f-f9bb1d7fc9e9</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>bb95b703-468a-4875-bfa8-3e859fb34178</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>62d373dd-5ef0-4189-a381-d616cbf6d57a</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.453754+09:00</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>소액사건 판결문의 현실</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">소액사건 판결문의 현실. </t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>prompter</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>bb95b703-468a-4875-bfa8-3e859fb34178</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>f6e91e4a-2bed-45ff-91fc-4348492862ab</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>bb95b703-468a-4875-bfa8-3e859fb34178</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>fd033f49-d279-4a57-8d75-598e7144f150</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.453754+09:00</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>소액사건 판결문에 대한 이야기경향신문의 승재현
+            한국형사, 법무정책연구원님 사례를 보았습니다. 동네 청년이 창업을 위해 모아둔 2000만원을 친구에게 빌려주었는데, 친구가 갚지 않아 민사소송을 제기했지만
+            패소했다고 합니다. 청년은 판결문을 읽어보았지만 그 이유를 알 수 없었습니다. 판결문에는 “원고의 청구를 기각한다. 소송비용은 원고가 부담한다”라는 두 줄만
+            적혀 있었다고 합니다. 연구위원님 말대로 “법이 그렇습니다”고 말할 수밖에 없습니다. 답답하기 그지없습니다.​법원에 가면 속시원히 모든 것을 가려줄 것이라는
+            기대가 있으실텐데, 실상은 다릅니다. 판결문을 받아봐도, 왜 이겼는지 졌는지를 알 수가 없습니다. 이런 경우는 정말 많습니다.소액사건의 정의와 간단한 판결문의
+            이유소액사건은 소송가액이 3,000만원을 초과하지 않는 민사사건을 의미합니다. 2021년 기준 최근 5년간 1심 민사 본안 사건은 매해 평균
+            98만1296건입니다. 이 중에서 소액사건은 71만691건으로 72.4%를 차지하고 있습니다. 법원에 있는 대부분의 사건이 소액사건이라고 봐도 될
+            겁니다.​소액사건이라고 마냥 간단하지도 않습니다. 소송가액이 적은 만큼, 절박한 당사자들이 변호사 없이 직접 법정에 나서서 두서 없이 하소연을 하는가 하면,
+            제출한 서면을 봐도 제3자는 도대체 무슨 소리인지 알기 어렵기도 합니다. 판사님들도 마찬가지 감정이라고 하더군요.사건 수에 비해 법관은 턱없이 적고, 사건은
+            적체되어 가니 소액사건심판법은 소액사건은 판결에 이유를 쓰지 않아도 된다고 규정하게 된 것입니다.​“판결서에는 민사소송법 제208조의 규정에 불구하고 이유를
+            기재하지 아니할 수 있다”(소액사건심판법 제11조의 2 제3항).​덕분에 절차도 빨라지고, 법원의 부담도 줄어들었습니다만, 문제는 위에서 본 청년처럼 판사님이
+            어련히 알아서 해주시겠거니 하고 제대로 소송을 하지 못하다 보면, 이유도 모른채 패소하기도 한다는 겁니다.3심제도와 항소의 어려움패소한 이후 항소하기도
+            어렵습니다. 우리나라 법제에서는 1심에 불만이 있는 경우 2심에서 다툴 수 있습니다. 다투기 위해서는 1심에서 ‘왜’ 패소했는지를 알아야 합니다. 판결문에
+            ‘이유’가 없다면 ‘왜’를 알 수 없습니다.​무엇을 가지고 항소를 한단 말인가요? 2021년 기준 최근 5년간 평균, 판결문에 판결이유가 기재된 경우 항소
+            비율은 22.3%에 이르고 있지만 소액심판사건 항소 비율은 4.1%에 그치고 있습니다. 이유가 없기 때문일 겁니다.​져도 이유를 알 수 없으니, 항소이유서를
+            써도 몇가지 패소 이유를 추측해서 집어넣을 수밖에 없습니다. 항소심 판사님도 받아보면 난감하기는 마찬가지 입니다.​개선 필요성과 대책이러한 문제점을 개선하기
+            위해 소액사건심판법에도 '이유'를 기재해야 한다는 개정안이 제출되었다고 합니다. 저는 소액사건을 다수 맡는 변호사로서 긍정적이라고 보기는
+            하지만, 법원의 사건 적체가 심각한 마당에 이유까지 쓰라면 재판 절차가 심각하게 늦어질 것도 우려됩니다. 3천만원 이하의 소액을 받는데도 일년을 끌어야
+            한다면요, 받아들이기 힘들 겁니다.​정책적인 해결방안은 그렇다 해도, 우리가 할 수 있는 것은 1심 소장 제출 시부터 꼼꼼하게 법적 주장을 담은 서면을
+            제출해서 승소판결을 받아보는 일입니다. ​저희 사무실에 의뢰하지 않으시고 혼자 소송을 하시는 경우에도 소장은 꼼꼼히 작성하시고, 제3자에게도
+            읽어보게 해서 다른 사람이 보았을 때도 수긍할만 한지 살펴보시길 권해드립니다.</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>assistant</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>bb95b703-468a-4875-bfa8-3e859fb34178</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>a48f7b0f-29ca-4a1a-a6f7-2ee63cc6631c</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>d6ccb73c-4735-4564-8928-6b6231939a22</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.453754+09:00</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>전세사기 공인중개사 손해배상청구 소송 진행 시 주의할 점</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전세사기 공인중개사 손해배상청구 소송 진행 시 주의할 점. </t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>prompter</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>a48f7b0f-29ca-4a1a-a6f7-2ee63cc6631c</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>0fe99d10-dfd5-4cb4-b58b-50f10bb6a63c</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>a48f7b0f-29ca-4a1a-a6f7-2ee63cc6631c</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>741b226c-7bc4-43f3-a85d-5015608697ae</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.453754+09:00</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>안녕하세요,​전세사기가 극심한 가운데 벌써
+            전세피해자로 인정된 분이 1만 9천명을 돌파했다는 보도를 보았습니다.​서민의 주거형태인 전세주택에는, 그동안 모아둔 목돈이 다 들어가 있거나, 사회초년생들이
+            은행이나 기관의 대출을 받아 마련한 큰돈이 들어가 있기 마련이고, 따라서 피해는 점점 극심해지고 있습니다.​최근 수사결과나 전세사기 상담사례를 살펴보면
+            공인중개사의 중개과실이 상당 부분 개입되어 있는 것을 볼 수 있습니다.​공인중개사는 중개하는 부동산에 대해 성실하고 정확한 법적 설명을 할 의무를 부담하고
+            있습니다(공인중개사법 제25조 제1항). 그럼에도 불구하고, 채무초과 상태인 부동산의 중개를 성사시킬 목적으로, 또는 임대인의 무리한 전세사기 계획에 가담할
+            목적으로 전세사기에 적극 가담하여 임차인을 유인하는 것인데요.​임차인은 공인중개사가 대상 부동산을 보여주는 것을 넘어서, 법적 위험성을 고지해주고 임대인과
+            원활하게 임대차계약을 체결하는 것을 도와줄 것이라고 당연히 기대하기 마련이고, 그러한 차원에서 중개수수료도 지급하고 있습니다.​그러나 일부 공인중개사 분들은
+            문제가 있는 부동산임에도 불구하고 허위 사실을 언급하며 임차인을 안심시키고, 부동산의 상황을 꾸며내어 기망하고, 임대인의 자력에 대한 근거 없는 보장을 하는
+            경우도 많은 것으로 보입니다.​전세사기 사건으로 발전되는 경우, 임대인은 보증금을 반환할 자력이 없다며 드러 눕는 경우가 많고, 경매를 진행해도 부동산
+            불경기로 인하여 보증금 전액을 받기에는 어려운 것이 현실입니다.​그런 때, 위와 같은 공인중개사의 불법적인 행위가 개입된 경우 당연히 공인중개사를 대상으로 한
+            손해배상청구소송을 진행할 수 있습니다.​그러나 손해배상청구소송 자체가 난이도가 높은 소송이라는 점은 반드시 염두해두셔야 합니다. 계약 체결 당시 공인중개사를
+            신뢰하고 별다른 자료를 남겨두지 않는 경우도 많고, 계약서를 제대로 보지 않는 경우도 있기에 공인중개사의 불법행위를 입증하기란 실무적으로 쉬운 일은 아닙니다.
+            ​제대로 된 증거가 없는데, 전세금을 돌려받지 못했다는 이유만으로 공인중개사를 상대로 민사소송을 제기하는 경우, 쉽게 패소판결이 나게 되고, 패소판결에 따라
+            상대방의 변호사 비용까지 물어주어야 하는 최악의 상황이 되기 마련입니다.​따라서 공인중개사를 대상으로 소송 제기 전에 주의하실 부분에 대해 몇가지 말씀을
+            드리고자 합니다.​첫번째, 형사고소절차를 활용하세요. 임대인과 공인중개사가 조직적인 범행을 저질렀던 정황이 확인되는 경우, 형사고소절차를 이용하여 경찰/검찰의
+            수사를 통해 공인중개사의 가담사실과 고의 또는 과실을 입증할 증거를 입수하세요.​두번째, 임대차계약서, 중개대상물 확인, 설명서를 꼼꼼히 읽어보세요. 서류 상
+            근저당권, 선순위 임차인에 대한 설명이 사실과 다르게 기재되어 있는 경우에는 손해배상청구소송의 주요 증거로 작용될 수 있습니다.​셋째, 변호사의 조력을
+            받으세요. 나홀로 소송을 진행하시는 경우도 많은데, 난이도가 높은 손해배상청구소송의 경우에는 변호사의 조력 하에 신중하게 접근하는 것이 필요합니다. 소송을
+            제대로 진행하지 못해 패소하는 경우에는 그 결과를 뒤집기가 매우 힘들고, 패소 시 상대방의 비용까지 물어주어야 하는 어려움이 있기 때문에 변호사 조력은 항상
+            처음부터 받으시는 것이 좋습니다.​</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>assistant</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>a48f7b0f-29ca-4a1a-a6f7-2ee63cc6631c</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>f7de852c-5841-4bf1-ad54-896ca76b1e4e</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>4e24e413-d9d4-4f7e-aa2e-e504bdf09eea</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.453754+09:00</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>과거 양육비 청구, 자녀 성인된 후 10년 지나면 못한다</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">과거 양육비 청구, 자녀 성인된 후 10년 지나면 못한다.. </t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>prompter</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>f7de852c-5841-4bf1-ad54-896ca76b1e4e</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>0fd65c91-f464-4a28-a536-3cff6b59c4d0</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>f7de852c-5841-4bf1-ad54-896ca76b1e4e</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>470b018b-1613-4e28-a718-2a63b8968f13</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.453754+09:00</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>We Solve 입니다. 2024. 7. 19.
+            매일경제에 아래와 같은 기사가 나왔습니다. 양육비 청구를 자녀가 성인된지 10년 안에 해야한다는 겁니다. 왜 성인된 이후부터 계산될까요? 왜 10년만 청구
+            가능할까요? 1심과, 2심, 3심 결론이 달랐던 판결을 토대로 지금부터 알아봅니다.Q) 변호사님, 양육비 청구는 이혼할 때 정하는 것으로 알고 있습니다.
+            협의이혼이든, 재판이혼이든 이때 정하는 거 아닌가요? 왜 뒤늦게 이런 소송이 생기는 건가요?A) 맞습니다. 이혼할 때 자녀가 미성년자라면 양육권을 정합니다.
+            이때 양육비도 함께 정하죠. 한쪽이 양육권을 가지면, 반대 쪽은 자녀가 성년이 될 때까지 매월 양육비를 지급해야 합니다. 이게 일반적입니다. 근데 이혼할 때
+            양육비를 제대로 안 정했거나, 별거 기간이 길어서 과거의 양육비를 나중에 청구하는 경우가 있습니다.Q) 양육비는 자녀가 미성년일 때 부모가 부담하는 걸로 알고
+            있습니다. 과거의 양육비는 언제부터 언제까지 청구하는 건가요?A) 혼인 중 부부라면 공동으로 양육 의무가 있습니다. 하지만 한쪽이 일방적으로 양육을
+            전담했다면, 해당 시점부터 자녀가 성년이 되는 시점까지 양육비를 소급해서 청구할 수 있습니다. 물론 입증이 가능해야 합니다. Q) 과거의 양육비 청구는 자녀가
+            성년이 된 이후 가능하다는 말씀이신가요?A) 맞습니다. 양육이 계속되는 동안에는 현재 또는 장래 양육비 청구는 가능하지만, 과거 양육비 청구는 불가하고요.
+            자녀가 성년이 되면 비로소 양육이 종료되므로 이때부터 과거 양육비 청구가 가능합니다.Q) 그렇다면 왜 성년된 이후 10년까지만 청구 가능하다고 대법원 판결이
+            나온 건가요?A) 민법상 일반 채권의 소멸시효가 10년입니다. 10년이 지나면 소멸시효가 적용돼서 행사를 못합니다. 대법원에서는 양육비도 일반 채권처럼 본
+            것입니다. 기산점은 위에 말씀드린대로 자녀가 성년이 된 시점으로 봤습니다.Q) 1심에서는 결론이 달랐다고 하는데요. 왜 1심과 대법원 판결이 결론이
+            달랐나요?A) 1심에서는 2011년 대법원 판결을 근거로 들었는데요. 자녀가 성년이 되었더라도 이혼 당시 협의나 법원 심판이 없었다면, 양육비 청구권이
+            사라지지 않는다는 이유입니다. 하지만 대법원은 협의 심판과 무관하게 과거 양육비 청구권은 존재하므로 시효기간이 시작된다는 것입니다.</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>assistant</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>f7de852c-5841-4bf1-ad54-896ca76b1e4e</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>c4cd0bc3-9f3e-4dc4-a9ee-3b35a349569c</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>8077419e-6777-4b00-98c4-2573c26db40f</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.453754+09:00</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>상속한정승인 및 상속포기의 방법</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상속한정승인 및 상속포기의 방법. </t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>prompter</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>c4cd0bc3-9f3e-4dc4-a9ee-3b35a349569c</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>3998e2b3-d8dd-442e-b566-023fbe068557</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>c4cd0bc3-9f3e-4dc4-a9ee-3b35a349569c</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>e3c2ba7a-4a4e-4618-8862-1c1bb3631273</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.454749+09:00</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>안녕하세요, ​새문안 법률사무소 김동현
+            대표변호사입니다.​갑작스러운 상속 문제에 마주한 분들을 위해, 상속한정승인 및 상속포기가 무엇이고, 어떻게 진행해야 하는지에 대해 살펴볼까
+            합니다.상속이란?​법률 용어부터 설명을 드려야 하겠습니다.​상속은 사람이 사망한 경우 그 사람이 가지고 있는 재산, 권리 및 의무가 법률에 따라 포괄적으로
+            승계되는 것을 의미합니다.​상속법은 사람의 사망에 따른 법률관계를 다루는 법으로, 민법 제5편 상속편에서 상세히 규정되어 있습니다.​상속은 사람이 사망하면
+            시작됩니다. 이를 '상속 개시'라고 하며, 상속의 개시라고 하면 자연인의 사망 시점을 가리킨다고 보시면 됩니다.​피상속인이란 사망한 자연인을
+            가리키는 말로, 상속을 받는 상속인과 대비되는 말입니다.​상속 순위는 민법이 정한 순서에 따라 상속인이 되는 순서를 의미하는데요, 피상속인이 사망하여 상속이
+            개시되면 다음 순서에 따라 상속인이 됩니다(민법 제1000조).제1순위: 피상속인의 직계비속(자녀) + 피상속인의 배우자제2순위: 피상속인의 직계존속(부모)
+            + 피상속인의 배우자제3순위: 피상속인의 형제자매제4순위: 피상속인의 4촌 이내 방계혈족이때 피상속인의 배우자는 제1순위나 제2순위 상속인이 있을 때는
+            공동상속인이 되고, 없다면 단독상속인이 되는 점이 독특합니다.​자 그렇다면, 본격적으로 상속이 개시되면 어떻게 상속재산을 확인하고 조치를 취해야 하는지
+            살펴보겠습니다.상속재산을 확인하는 방법상속이 개시되면 상속인들은 3개월의 기간이 있음을 알고 조치를 취해야 합니다.​상속인들은 3개월 동안 피상속인이 남긴
+            재산상황이 어떤지 자세히 확인하고, 그대로 이어받으려면 단순승인, 한정승인, 포기를 선택해야 합니다.​그러나 망인이 어떤 재산이 있는지, 부채가 있는지를
+            알아낸다는 것은 쉬운 일은 아닙니다. 정부에서는 상속재산을 조회해볼 수 있는 제도를 두고 있는데, 자세히 말씀을 드려보겠습니다.금융감독원 상속인금융거래조회
+            서비스가까운 은행, 농협, 수협, 우체국에 방문하여 신청하면, 금융채권(예금, 보험, 예탁증권, 공제 등) 및 채무, 각종 주식, 일정액 이상의 조세나 과태료
+            체납사실을 조회할 수 있습니다. 약 7~20일이 소요됩니다.​준비서류는 사망일 및 주민등록번호가 기재된 기본증명서, 사망진단서 등 사망자 기준
+            가족관계증명서(최근 3개월 내 발급, 주민등록번호 기재) 또는 가족관계증명서, 상속인 신분증입니다. 망인의 사망 뒤 서류를 떼기가 어려운 경우가 있으니,
+            가시기 전에 지점에 먼저 전화해보고 가시면 좋겠습니다.​안심상속 원스톱서비스가까운 시청, 구청, 읍/면/동 주민센터를 방문하여 신청할 수 있습니다.
+            정부24(https://www.gov.kr )에서는 온라인 신청도 가능합니다. 금융거래조회, 국민연금 가입여부, 공무원/사학/군인연금 가입여부, 국세 및
+            지방세 정보, 토지/건축물/자동차 소유 여부를 확인할 수 있습니다. 약 7~20일이 소요됩니다. ​행안부에서 한번의 통합 신청으로 금융거래 및 재산을 확인할
+            수 있게 되었고, 주민센터에서는 사망신고 시점에 동 서비스에 대해 자세히 알려줄 것이기 때문에 한번에 신청하시면 좋습니다.​사망신고는 피상속인의 사망 후
+            1개월 내 하셔야 하기 때문에, 안심상속 원스톱서비스를 바로 신청하시면 좋습니다. 자동차, 건축물 정보는 바로 알려줄텐데 기타 금융거래나 국민연금 등은 추후
+            지정하신 방법으로 알려줄 것입니다.​자 그렇다면, 피상속인의 재산상황에 대해 전체적으로 파악해보셨을때 고려하셔야 하는 것은, 적극재산(+인 재산)보다
+            소극재산(-인 재산)이 많은지를 살펴보셔야 합니다. 한마디로 전부 상속을 받는다면 채무가 더 많게 되는 경우는 아닌지를 살펴보셔야 하는 것입니다. 이를
+            '채무초과'상태라고 합니다. 채무초과 상태에서 상속을 '단순승인'하게 되면 재산과 함께 채무도 전부 상속받게 되므로 주의하셔야
+            합니다.상속의 단순승인을 하면 안되는 경우채무초과 상태가 되는 경우에는, 상속인은 피상속인의 상속재산을 승계하기를 원하지 않을 것입니다. 이때 상속인은 상속의
+            개시가 있음을 안 날로부터 3개월 내 가정법원에 상속의 한정승인 또는 상속포기의 심판을 청구할 수 있습니다.​한정승인이란, 피상속인으로부터 상속받은 재산의
+            한도 내에서 피상속인의 채무와 유증을 변제할 것을 조건으로 상속을 승인하는 것입니다.​상속포기란, 상속개시로 인해 상속인이 된 사람이 상속에 따른 재산의
+            승계를 거부하여 처음부터 상속인이 아닌 것이 되는 것입니다.​다만 유의하실 점이 있습니다. 적극재산이 거의 없고 소극재산만 있는 경우 상속포기를 한다고 끝나지
+            않습니다.​선순위 상속인 중 일부가 상속을 포기하면 상속분은 나머지 상속인들에게 비율에 따라 귀속됩니다. 그러나 선순위 상속인 전원이 상속을 포기해버리면 다음
+            순위 상속인들에게 상속되게 되고, 그 다음 순위 상속인들도 포기한다면 그 다음 순위의 상속인에게 상속됩니다. 이때 제4순위 상속인들까지 전원 상속을 포기해야
+            하는 상황이 벌어지는데, 문제는 가족이 많은 경우 수십명이 함께 상속을 포기해야 하는 경우도 빈번하게 발생한다는 점입니다.​따라서 실무 상으로는 일부만 상속을
+            포기하고, 상속인 중 한명이 한정승인을 하여 상속을 종결하는 방식을 활용하게 됩니다. 주의하실 점은 직계비속(자녀들)이 상속포기를 하고 배우자가 한정승인을
+            하기도 하는데, 이 경우에는 직계존속(부모)와 배우자가 공동상속인이 되는 결과가 되므로 꼭 주의가 필요합니다.​상속한정승인 심판청구의 방법상속한정승인을 하려는
+            경우, 법원의 상속한정승인 심판을 받아야 합니다. 피상속인의 마지막 주민등록 상 주소지를 관할하는 가정법원(서울은 서울가정법원, 그외 지역은 지방법원/지원,
+            외국이라면 서울가정법원)에 청구서를 제출하여야 합니다.​한정승인심판에서 중요한 것은 반드시 상속재산목록을 작성해서 제출해야 한다는 점입니다. 위에서 말씀드린
+            안심상속 원스톱서비스를 활용하세요.​상속재산목록은 적극재산(+인 재산)과 소극재산(-인 재산)을 나눠서 기재해야 하고, 고의적으로 상속재산목록의 항목을 빠뜨린
+            경우에는 민법에 따라 단순승인을 한 것으로 보게 될 수 있으니 반드시 주의하시기 바랍니다.​만일 재산의 전체적인 내용을 파악하는데 시간이 오래 소요되는
+            경우에는 3개월 간 기간을 연장해달라고 청구할 수 있습니다. 따라서 망인의 사망 후 3개월 내에 일단 어떤 조치든 취해야 한다는 점을 고려해주세요.​한정승인이
+            수리되면, 상속인은 상속채권자와 유증을 받은 수유자에 대하여 한정승인 신고가 수리된 사실과, 2개월 내 기간 동안 채권 또는 수증을 신고할 것을
+            신문공고해야합니다. 피상속인의 주소지를 관할하는 일간신문에 1회 이상 공고하여야 합니다.​공고기간 동안은 채권자의 변제요청을 거절할 수 있고(민법
+            제1033조), 기간 동안 신고한 채권자들에게 상속인은 순위에 따라 배당변제를 하게 됩니다.​채권자가 한정승인한 상속인을 상대로 상속채무를 이행하라고 소송을
+            제기하는 경우도 있습니다. 이때 상속인은 한정승인을 했으므로 '한정승인의 항변'을 하여야 합니다. 그렇다면 상속재산의 범위 내에서 지급하라는
+            판결이 이루어지게 됩니다.​만약 상속인이 가진 고유한 재산을 대상으로 강제집행이 이뤄지려는 경우에는 제3자이의의 소송을 제기하여 불복할 수 있습니다. 만일
+            소송의 변론종결시점 이후에 한정승인이 이루어졌다면 청구이의의 소를 제기하여 불복할 수 있습니다.상속포기 심판청구의 방법상속포기를 하려는 경우, 법원에 상속포기
+            심판을 받아야 합니다. 피상속인의 마지막 주민등록 상 주소지를 관할하는 가정법원에 청구서를 제출하여야 합니다.​상속포기심판에서는 상속재산목록을 작성해서 제출할
+            필요는 없으나, 앞에서 말씀 드렸던 것처럼 (1) 후순위 상속인들에게 계속 상속이 이뤄질 수 있으니 한정승인을 활용할 필요가 있는 점, (2) 배우자의 경우
+            상속순위 문제가 있어 직계존속에게 상속이 될 수 있다는 점을 유의하셔서 두 제도를 함께 이용하실 필요가 있습니다.​상속한정승인, 상속포기 시 주의사항간혹
+            상속포기, 한정승인을 청구하면서도 다음과 같이 상속재산을 정리하시기도 하는데 절대 하시면 안됩니다. 민법에 따라 상속을 단순승인한 것으로 간주되어 한정승인과
+            상속포기를 받더라도 무효가 될 우려가 있습니다.​예금 출금채권 수령, 추심임대차 보증금 수령재산을 소비하거나 매각하는 일임대차 재계약</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>assistant</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>c4cd0bc3-9f3e-4dc4-a9ee-3b35a349569c</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>b842849c-1f5b-4a8b-bcf6-fa1f8724335c</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>c419d33f-26da-4347-846e-097fedeacd39</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.454749+09:00</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>유튜버 쯔양 사건으로 보는 공갈죄와 협박죄의 차이는?</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">유튜버 쯔양 사건으로 보는 공갈죄와 협박죄의 차이는?. </t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>prompter</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>b842849c-1f5b-4a8b-bcf6-fa1f8724335c</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>4d7a66b0-811d-4f93-baa3-b9d9bc2b6925</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>b842849c-1f5b-4a8b-bcf6-fa1f8724335c</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ef086899-a8fa-46e7-963e-c642a270629a</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.454749+09:00</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>안녕하세요. 가장 두렵고 어려운 순간, 의뢰인의 곁에
+            함께 하는 법률사무소 화해입니다.​누구나 한 번쯤 ‘공갈’, ‘협박’이라는 단어를 들어봤을 것입니다. 어떤 분들은 ‘공갈협박’이라고 한 단어로 쓰기도
+            하는데요. 현행법상 공갈협박이라는 죄명은 존재하지 않으며 ‘공갈죄’와 ‘협박죄’는 각각 다른 범죄로서 존재하고 있습니다.​최근 유명 유튜버 쯔양 사건을
+            아시나요? 처음에는 쯔양이 전 남자친구이자 소속사 대표였던 A씨에게 4년간 지속적인 폭행, 협박, 상해, 불법 촬영, 40억 착취 등의 피해 사실을 폭로하며
+            고소 사실을 알렸는데요. 이후 쯔양 남자친구는 극단적 선택으로 사망하며 사건은 공소권 없음으로 불송치되면서 처벌을 할 수 없게 되어 이대로 종결되는 듯
+            보였습니다.​그러나 이후 쯔양의 과거를 폭로하지 않겠다는 조건으로 5,500만 원의 계약을 체결한 혐의의 유튜버 구제역과 수천만 원 뜯어낸 혐의를 받는 렉카
+            연합 소속 유튜버들, 구제역에게 쯔양의 과거와 허위 사실을 제보한 인물이 다름 아닌 쯔양의 전 남자친구의 담당 변호사였다는 사실이 밝혀지면서 연일 큰 논란이
+            되고 있는데요.​쯔양은 본인의 라이브 방송에서 협박 정황이 담긴 증거를 공개하기도 했습니다. 각종 동영상, 대화 녹취록, 이메일 내용이 공개되면서 이들의 실형
+            가능성과 협박죄 또는 공갈죄의 구성요건을 두고 여러 의견이 나오고 있는 상황인데요.​오늘은 그 뜻이 비슷해 공갈협박이라고도 불리는 공갈죄·협박죄의 성립 요건과
+            처벌 수위에 대해 알아보도록 하겠습니다.| 협박죄협박죄는 사람을 위협하거나 공포를 느끼게 하여 타인의 의사결정이나 행동의 자유를 침해하는 범죄입니다. 협박이란
+            상대방에게 두려움을 주기 위해 해를 끼치겠다고 위협하는 행위를 말하는데요.​ 성립 요건· 공포심 유발할 정도의 해악을 고지· 고지한 해악이
+            이루어질 가능성​협박은 생명, 신체, 자유, 재산, 신용 등 모든 부분의 해악이 포함되며 본인에게 직접적으로 해악을 고지하는 경우는 물론 상대방과 밀접한
+            관련이 있는 타인에 대하여도 해악을 고지할 수 있습니다. 또한 협박 당시 본인이 해악을 느끼지 못했다고 하더라도 상대방에게 공포심을 유발했다면 성립할 정도로
+            폭넓게 인정하고 있습니다.​특히나 협박은 받아들이는 사람에 따라 해석이 달라져 비슷해 보이는 사건이라도 결과가 천차만별이기 때문에 협박죄의 혐의를 받고 있다면
+            법률전문가의 도움을 받아 보시기를 권해드립니다.​​ 처벌 수위_______________________제283조(협박, 존속협박) ①사람을 협박한 자는 3년
+            이하의 징역, 500만원 이하의 벌금, 구류 또는 과료에 처한다.②자기 또는 배우자의 직계존속에 대하여 제1항의 죄를 범한 때에는 5년 이하의 징역 또는
+            700만원 이하의 벌금에 처한다.③제1항 및 제2항의 죄는 피해자의 명시한 의사에 반하여 공소를 제기할 수 없다. 제284조(특수협박) 단체 또는 다중의
+            위력을 보이거나 위험한 물건을 휴대하여 전조제1항, 제2항의 죄를 범한 때에는 7년 이하의 징역 또는 1천만원 이하의 벌금에
+            처한다._______________________| 공갈죄공갈죄는 사람을 폭행하거나 협박하여 재물의 교부를 받거나 재산상의 이익을 취득하는 범죄입니다. 이러한
+            공갈죄는 폭행 또는 협박을 수단으로 하여 행위가 이루어진 경우 성립하는 범죄이기 때문에 협박죄와 혼동하기 쉬운데요. 여기서 ‘공갈’이란 재물 또는 재산상의
+            이익을 취득할 목적으로 폭행 또는 협박으로 상대방의 의사에 제한을 가하는 정도로 충분하며, 반드시 상대방의 반항을 불가능하게 할 정도일 필요는 없다는 점이
+            중요합니다.​​ 성립 요건· 협박이나 폭행의 사실(공갈행위)· 다른 사람에게 공포심을 유발· 이로 인해 재물의
+            교부 및 재산적 이익(처분)이 있어야​위 3가지 요건이 인정될 경우 공갈죄가 성립할 수 있습니다. 이때 실제로 ‘타인의 재물이나 재산상의 이익을 취득’해야
+            하는데요. 공포심을 일으킨 대상과 재물을 교부한 대상이 다르거나, 제3자가 재물을 받은 경우에도 성립됩니다. ​​ 처벌
+            수위_______________________제350조(공갈) ①사람을 공갈하여 재물의 교부를 받거나 재산상의 이익을 취득한 자는 10년 이하의 징역 또는
+            2천만원 이하의 벌금에 처한다.②전항의 방법으로 제삼자로 하여금 재물의 교부를 받게 하거나 재산상의 이익을 취득하게 한 때에도 전항의 형과 같다.
+            제350조의2(특수공갈) 단체 또는 다중의 위력을 보이거나 위험한 물건을 휴대하여 제350조의 죄를 범한 자는 1년 이상 15년 이하의 징역에
+            처한다._______________________| 협박죄·공갈죄의 차이점공갈죄와 협박죄의 가장 큰 차이는 협박 행위가 상대방의 ‘의사결정의 자유나 행동의
+            자유를 침해할 목적으로 행해졌는지’와 ‘재물 또는 재산상의 이익을 취득할 목적으로 행해졌는지’인데요. 전자는 협박죄를 후자는 공갈죄를 구성하는 요건으로 이에
+            따라 성립하는 범죄, 처벌 수위가 달라집니다.​또한 공갈죄는 미수범 규정으로 재산상 이득을 취득하지 못했더라도 공갈죄와 동일한 처벌 수위를 받게 되며,
+            협박죄는 반의사불벌죄로 피해자가 처벌을 원하지 않는다는 의사를 명백히 했다면 본 죄로 벌할 수 없으며 고소한 사건을 취하했다면 다시 (재)고소할 수
+            없습니다.이처럼 형사사건은 초기 전략과 대응이 중요합니다. 특히 공갈죄·협박죄 고소는 상대방의 생각이라는 주관적인 요건에 따라 혐의 성립의 가능성이 달라지므로
+            자신이 그러할 의도가 없었다고 할지라도 상대방이 그렇게 느꼈다면 혐의가 성립할 수도 있습니다. 그렇기 때문에 협박죄·공갈죄 고소로 억울한 상황에 처해있다면
+            법률사무소 화해 형사 전문변호사와 상담하셔서 부당하게 형사처벌로 이어지지 않도록 빠른 도움을 받으시길 바랍니다.</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>assistant</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>b842849c-1f5b-4a8b-bcf6-fa1f8724335c</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>b9a76e24-373d-43f2-82ff-1495553d61ad</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>92832e7a-859b-409f-a50e-59815339fad5</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.454749+09:00</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>협의이혼에 관하여</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">협의이혼에 관하여. </t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>prompter</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>b9a76e24-373d-43f2-82ff-1495553d61ad</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>8120cf74-bbe2-451f-9966-d667f07c6d45</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>b9a76e24-373d-43f2-82ff-1495553d61ad</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1f68fad4-ce02-4f28-977e-a18ce581e986</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.454749+09:00</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>안녕하세요. 김상헌
+            변호사입니다.    2023년에 9만 2,394건의 이혼이 있었을 만큼, 이혼은 더 이상 낯선 현상이
+            아닙니다. 주위에 이혼했거나 이혼하려는 부부가 적지 않다 보니, 협의로 원만하게 혼인관계를 종료시키는 협의이혼에 관해 궁금해하시는 분들도
+            늘어났습니다.  이혼의 종류는 크게 협의이혼과 재판상 이혼이 있습니다. 부부가 이혼 의사의 합치에 이르면 협의이혼을 할 수 있고, 일방이라도
+            이혼에 반대하는 경우에는 법원의 재판으로 이혼을 할 수 있습니다. 2023년 기준 전체 이혼 건수 중 협의이혼 건수는 약 7만 2천건, 재판상 이혼 건수는 약
+            2만건으로, 이혼을 하는 경우 대다수가 협의이혼을 한다는 사실을 확인할 수 있습니다. 협의이혼은 부부가 관할 가정법원에서 협의이혼의사 확인을
+            받은 후, 위 확인서등본을 첨부하여 주소지 관할 시청·구청·읍사무소 등에 이혼신고를 함으로써 그 효력이 발생합니다(민법
+            제836조 참조).    당사자들 간에 특별한 다툼이 없는 한 협의이혼은 가장 신속한 이혼
+            방법입니다. 양육하여야 할 자녀(포태중인 자녀 포함)가 있는 경우 협의이혼신청서 접수 후 숙려기간인 3개월이 지나면 이혼이 성립되고,
+            양육하여야 할 자녀가 없는 경우에는 신청서 접수 후 1개월이 지나면 이혼이 성립됩니다(민법 제836조의2 제2항 참조).  통상 이혼을 할
+            경우 부부가 정해야되는 사항은 미성년 자녀가 있을 경우, 양육에 관한 사항, 재산분할 및 위자료입니다.  미성년 자녀가
+            있다면, 부부는 양육자의 결정, 양육비용의 부담, 면접교섭권의 행사 여부 및 방법 등에 관한 사항을 정하여야 하고, 이혼 확인을 받을 때 법원에 협의서를
+            제출하여야 합니다(민법 제837조 참조).   법원에서 확인해주는 사항은 이혼의사와 미성년 자녀 양육에 관한 사항 뿐이므로,
+            부부는 협의이혼신고를 할 때 반드시 재산분할 및 위자료까지도 정해야 하는 것은 아닙니다. 만약 재산분할 및 위자료에 관해
+            협의가 이루어지지 않는다면, 이혼한 날로부터 2년 이내에 가정법원에 재산분할을 청구할 수 있고(민법 제839조의2 참조), 손해 및 가해자를
+            안 날로부터 3년 이내에 위자료를 청구할 수 있습니다(민법 제766조 참조).</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>assistant</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>b9a76e24-373d-43f2-82ff-1495553d61ad</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ed2e6c30-b4cd-4525-84f4-39955dca89cf</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1da5a3df-b39d-45d9-b8a5-57fb67ccf2ba</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.454749+09:00</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>상속부동산을 팔아서 상속채무를 갚으면 단순상속으로 간주되나요?</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상속부동산을 팔아서 상속채무를 갚으면 단순상속으로 간주되나요?. </t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>prompter</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>ed2e6c30-b4cd-4525-84f4-39955dca89cf</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>7fc1280b-304b-4f79-abb1-a2d3e44b0d62</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ed2e6c30-b4cd-4525-84f4-39955dca89cf</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>fb35c680-8c53-472a-b136-3d6a6f203dc0</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.454749+09:00</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>﻿﻿﻿﻿﻿1. 한정승인과 단순승인상속
+            시 한정승인은 상속인이 상속재산 내에서 상속채무를 변제하는 것을 의미하며, 단순승인은 상속인이 상속채무와 상속재산 모두를 무조건 승계하는 것을 말합니다.
+            한정승인은 상속재산의 과다한 채무를 피하기 위해 선택할 수 있는 방법입니다.2. 단순승인으로 ﻿간주하는 경우상속인이 상속재산을 임의로 처분하거나, 상속재산을
+            은닉, 은폐, 부정사용한 경우 단순승인으로 간주됩니다(민법 제1026조). 이는 상속인이 상속재산을 보호하고 관리할 의무를 저버리는 행위로 간주되기
+            때문입니다.3. 상속재산을 처분하면 모두 단순승인으로 간주되는가?앞서 "상속인이 상속재산에 대한 처분행위를 한 때"에는 단순승인으로 간주될
+            수 있는데,  법원은 이에 대한 시간적 제한을 두고 해석하고 있습니다(대법원 2003다63586 판결 참조).법원에 따르면 "민법
+            제1026조 제1호는 상속인이 한정승인 또는 포기를 하기 이전에 상속재산을 처분한 때에만 적용하는 것"이기 때문에, "한정승인 또는 포기를
+            한 후 상속재산을 처분한 때에는 그것이 같은 조 제3호에 정한 상속재산의 부정소비에 해당되는 경우에만 상속인이 단순승인을 한 것으로 보아야 한다"는
+            것이죠.4. 부정사용에 해당﻿하지 않기 위한 요건그렇다면 민법 제1026조 제3호의 '부정소비'는 무엇을 의미할까요? 법원은 "정당한
+            사유 없이 상속재산을 써서 없앰으로써 그 재산적 가치를 상실시키는 행위"를 부정소비라고 보고 있습니다.이렇게 말로만 들어서는 잘 와닿지는 않죠. 쉽게
+            말하면 팔았다고 해서 바로 부정소비가 되는 것은 아니고, 판 금액을 상속채무 변제에 사용하지 않고 개인적 목적 등으로 유용한 경우에 비로소 부정소비에
+            해당한다는 것입니다.5. 상속재산을 최대한 지키면서 상속채무﻿를 변제할 방법위 내용들을 종합하면, 가장 효율적으로 상속채무를 변제할 방법을 떠올릴 수
+            있습니다. 즉, 상속채무를 갚기 위해 상속재산인 부동산을 경매에 부치는 경우 일반적인 시세보다 낮게 형성되는 것은 당연하고 어쩌면 수 차례
+            유찰을 거친 뒤 반 토막이 난 가격으로 낙찰되는 경우도 허다합니다.부모님께서 물려주신 소중한 상속재산의 절반을 경매 절차에서 날려버리게 되는 것이죠.그렇기에
+            상속재산을 바로 경매에 부치지 말고, 상속인(가능하면 1인이 한정승인을 하는 경우가 좋겠죠)이 해당 부동산에 대하여 상속등기를 경료한 뒤, 제3자에게 합리적인
+            가격을 매매하는 방법을 고려해보셔야 합니다.물론 매매 후 그 대금을 한 통장에 받아두고 상속채무가 모두 변제될 때까지 절대 다른 곳에 유용해서는
+            안되겠죠.아울러 항상 유의하셔야 할 것은 상속재산을 처분할 때 상속채무 변제를 위한 정당한 목적이 있어야 하며, 처분 과정이 투명하고 합리적이어야 합니다.
+            법원에 처분 계획을 제출하거나, 상속채무 변제를 위한 매매임을 입증할 수 있는 자료를 준비하는 것도 좋습니다.5. 결﻿론상속재산 처분 시 한정승인이
+            단순승인으로 간주되지 않도록 주의가 필요합니다. 상속채무 변제를 위한 정당한 목적으로 투명하게 처분 절차를 진행한다면 단순승인 위험을 줄일 수 있습니다.
+            법률적 자문을 통해 안전하게 상속재산을 처분하시기 바랍니다.﻿</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>assistant</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>ed2e6c30-b4cd-4525-84f4-39955dca89cf</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>f8b10257-8ece-40e8-b596-86b2387f0418</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>925eb822-5cc8-49aa-8b25-0b3b48846d2f</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.454749+09:00</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>비 오는데 우산 없다고 이러시면 큰일나요!</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비 오는데 우산 없다고 이러시면 큰일나요!. </t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>prompter</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>f8b10257-8ece-40e8-b596-86b2387f0418</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2b82cb81-24ec-484b-af9e-406d45645b9f</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>f8b10257-8ece-40e8-b596-86b2387f0418</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>4c596695-6518-4a92-b1e7-19a76b2bc1bb</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.454749+09:00</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Focus ON - 비오는데 우산 없다고 몰래
+            가져가면 큰일나요!장마철, 누구나 한번쯤 할 수 있는 실수?로톡 상담사례에서는 위에서 소개한 USB를 습득했다가 절도범으로 몰린 경우 말고도 절도죄로 몰린
+            다양한 사례를 확인할 수 있습니다. 특히 장마철에는 우산 분실/절도 관련 사례가 많은데요. 먼저, 아래 로톡뉴스 기사의 내용을 확인해볼까요?다른 손님에게
+            우산을 도둑맞은 A씨는 식당 CCTV를 확인하고 나서는 ‘우산 도둑’ B씨를 신고할 수 밖에 없었습니다. B씨는 우산꽂이에서 A씨의 우산을 꺼내 들어 돌려보고
+            내려놨는데, 잠 시 뒤 일행과 이야기를 나누면서 그 우산을 다시금 집어갔습니다. 이러한 행동에서 A씨는 “고의로 가져갔다”고 확신했습니다.사안을 검토한
+            변호사들은 “실제 B씨의 우산과 A씨의 우산이 유사하지 않다면, 절도의 고의가 인정될 가능성이 매우 높다”라는 의견을
+            냈습니다.&amp;gt;&amp;gt; 로톡뉴스 기사로 확인하기절도죄 vs. 사용절도죄 vs. 점유이탈물횡령죄일반적으로 절도라고 생각할 수 있는
+            행동에 대해서도 그 상황에 따라 다른 범죄로 분류가 되는데, 각각의 정의에 대해 알아보겠습니다.[절도죄] - 형법 제329조타인의 재물을 절취하는 행위로서,
+            타인이 점유하는 재물을 그 의사에 반하여 점유를 배제하고 자기 또는 제3자의 점유로 옮기는 것을 말함- 영구적으로 재물의 경제적 이용을 목적으로 함- 6년
+            이하의 징역 또는 1천만원 이하의 벌금에 처함- 상습절도의 경우 특정범죄 가중처벌 등에 관한 법률 제5조의4에 의해 가중처벌됨[사용절도죄] - 형법
+            제331조의 2타인의 자동차, 선박, 항공기 또는 원동기장치자전차를 일시 사용할 목적으로 탈취하는 행위- 일시 사용할 의사로 타인의 점유를 배제하고 자기 또는
+            제3자가 사용하는 것- 3년 이하의 징역, 500만원 이하의 벌금, 구류 또는 과료에 처함[점유이탈물횡령죄] - 형법 제 360조유실물, 표류물 기타 점유를
+            이탈한 타인의 재물을 횡령하는 행위- 타인의 점유를 이탈한 재물에 대해 새로운 점유를 개시하고 불법영득의 의사로 자기 것처럼 처분하는 것- 1년 이하의
+            징역이나 300만원 이하의 벌금에 처함- 절도죄와 달리 타인의 점유 하에 있던 물건이 아니라는 점에서 구별됨각 죄의 핵심 요소를 보면, 절도죄는 타인 점유
+            재물의 절취, 사용절도죄는 특정 재물의 일시 사용 목적 탈취, 점유이탈물횡령죄는 점유 이탈 재물의 불법 영득이라 할 수 있습니다.절도죄와 사용절도를 가르는
+            기준, 불법영득의사절도죄와 사용절도죄는 모두 타임의 재물을 무단으로 탈취한다는 공통점이 있습니다. 하지만, 절도죄는 타인 재물에 대한 불법영득의 의사, 즉 그
+            물건을 자기 소유물과 같이 그 경제적 용법에 따라서 이용하고 처분할 의사가 필요합니다.반면, 사용절도란 타인의 재물을 일시적으로 사용한 후에 소유자에게
+            반환하는 것으로서, 반환의사를 그 본질적인 요소로 합니다. 예를 들어 잠깐 복사만 한 후에 돌려줄 의사로 서류를 절취한 때에는 사용절도입니다. 자동차, 선박,
+            항공기, 원동기장치자전거 등 특정 재물로 제한되는데, 대법원은 일관하여 "일시 사용의 목적으로" 자전거나 자동차를 타고 간 때에는
+            불법영득의사를 인정할 수 없다(즉 절도죄가 인정되지 않는다)는 입장입니다.</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>assistant</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>f8b10257-8ece-40e8-b596-86b2387f0418</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>245573b4-adea-4be4-a413-082d72911122</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>bb04255f-d6da-4367-80b7-9aa543ec88e7</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.454749+09:00</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>너무 급한 나머지, 정말 실수로 여자 화장실에 들어갔어요ㅠ</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">너무 급한 나머지, 정말 실수로 여자 화장실에 들어갔어요ㅠ. </t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>prompter</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>245573b4-adea-4be4-a413-082d72911122</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2d99002b-3087-41f1-bdc1-487197290733</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>245573b4-adea-4be4-a413-082d72911122</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2f457c64-de3c-4200-9798-5ac4ae7d5cd4</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.455746+09:00</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Focus ON - 다중이용장소(공공장소) 침입
+            행위남성이 여성 전용공간에 들어가면 무조건 처벌 받나?최근 ‘동탄 화장실 사건’이라며 온라인을 떠들썩하게 한 사건이 있습니다. 20대 남성 A씨가 자신이 사는
+            아파트의 헬스장 옆 관리사무소 건물 내 여자 화장실에서 50대 여성 B씨가 용변을 보는 모습을 훔쳐보고 성적 행위를 했다는 혐의로 강제추행 혐의로
+            입건되었습니다.경찰에서는 “A씨가 여자화장실에 들어간 CCTV영상이 있다”고 주장했는데, 조사가 진행되면서 B씨가 “허위신고를 했다”고 자백하여 무혐의로
+            종결되었습니다.A씨는 누명을 쓰게 된 경우인데, 만약 실제로 여자 화장실에 들어갔다면 어떻게 처벌될 수 있을까요? 이와 유사한 상담 사례는 로톡에서도 많이
+            찾아 볼 수 있습니다. 남자가 실수로 여자탈의실이나 여자화장실에 들어갔다가 잘못됨을 인지하고 나왔는데, 그곳을 이용하려는 여자와 마주쳤거나 입구에 설치된
+            CCTV에 그 장면이 찍혔다는 내용입니다. 변호사들의 답변을 살펴보면 공통적으로 ‘성적 욕망을 만족시킬 목적’이 있어야만 관련법으로 처벌된다고 말하고
+            있습니다. 실수로 침입한 행위에 대해서는 지나치게 걱정하지 않아도 되겠습니다.&amp;gt;&amp;gt; 상가 여자화장실에 13차례 들락날락
+            했으나 무죄를 선고받은 남성 사례 기사로 확인하기다중이용장소 침입행위의 처벌은 어떻게 달라지나?[성폭력범죄의 처벌 등에 관한 특례법 제12조]는 자기의 성적
+            욕망을 만족시킬 목적으로 화장실 등 불특정 다수가 이용하는 다중이용장소에 침입하거나 같은 장소에서 퇴거요구에 불응하는 행위를 처벌하고 있습니다. 이는 성적
+            동기에 기한 침입행위 자체를 처벌하기 위한 조항입니다.제12조(성적 목적을 위한 다중이용장소 침입행위)자기의 성적 욕망을 만족시킬 목적으로 화장실,
+            목욕장ㆍ목욕실 또는 발한실(發汗室), 모유수유시설, 탈의실 등 불특정 다수가 이용하는 다중이용장소에 침입하거나 같은 장소에서 퇴거의 요구를 받고 응하지
+            아니하는 사람은 1년 이하의 징역 또는 1천만원 이하의 벌금에 처한다. [개정 2017. 12. 12., 2020. 5. 19.]최근 2년간 남성이 위 조항
+            위반으로 처벌받은 사례들을 살펴보면, 단순히 성적 목적으로 여성 화장실에 침입한 경우보다 침입 후 불법촬영 등 추가 범행까지 저지른 경우 처벌 수위에 차이가
+            있음을 알 수 있습니다.단순 침입만 한 사례로 대전지방법원 2014고단1068 판결을 들 수 있는데, 피고인이 여자화장실에 침입하여 고개를 숙여 옆 칸에서
+            용변을 보는 여성들의 모습을 지켜본 사안에서 벌급 300만원이 선고 되었습니다.</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>assistant</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>245573b4-adea-4be4-a413-082d72911122</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>929074f3-3a1d-4dbc-b51a-82778987af58</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ef709ce7-549c-48a9-9cc9-4c22eea3bc63</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.455746+09:00</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>후회</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">후회..하고 있어요. 성매매 했던 그날을. </t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>prompter</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>929074f3-3a1d-4dbc-b51a-82778987af58</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>23727283-8ec8-41d7-b311-f5865b95374b</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>929074f3-3a1d-4dbc-b51a-82778987af58</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>7ccee63d-617b-4eab-9e0e-2e08912163c9</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2024-07-24T17:09:35.455746+09:00</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Focus ON - 성매매 초범이거나 자수한다면 선처
+            받을 수 있나?성매매 처벌 규정‘성매매알선 등 행위의 처벌에 관한 법률’에서 정의하는 성매매는 아래와 같습니다.제2조(정의)1. “성매매”란 불특정인을 상대로
+            금품이나 그 밖의 재산상의 이익을 수수(收受)하거나 수수하기로 약속하고 다음 각 목의 어느 하나에 해당하는 행위를 하거나 그 상대방이 되는 것을 말한다.가.
+            성교행위나. 구강, 항문 등 신체의 일부 또는 도구를 이용한 유사 성교행위간혹 ‘건전마사지샵 인 줄 알았다’, ‘마사지만 받았을 뿐 성관계는 갖지 않았다’며
+            무죄를 주장하는 경우가 있는데, 유사 성행위도 함께 처벌됩니다. ‘키스방’과 같은 신종 변태업소의 경우 성매매에 해당하는지 논란이 있지만, 말 그대로의 키스를
+            넘어 유사성행위에 해당하는 경우라면 성매매로 처벌받을 수 있습니다.성매매에 해당한다면 아래의 벌칙에 따라 처벌됩니다.제21조(벌칙)① 성매매를 한 사람은 1년
+            이하의 징역이나 300만원 이하의 벌금ㆍ구류 또는 과료(科料)에 처한다.하지만 위의 경우는 성매매 혐의가 인정되고, 초범이라 하더라도 증거가 있을 경우에
+            해당합니다. 만약 성매매를 위해 연락을 취했거나 업소에 방문했다가 마음이 바뀌어 실제 성행위, 유사행위에 이르지 않았다면, 성매매 미수로 분류되어 처벌하지
+            않습니다. 우리법에 타인의 성을 사고자 하거나, 타인에게 성을 팔고자 시도했던 행위에 대한 처벌 규정은 아직 존재하지 않기
+            때문입니다.&amp;nbsp;성매매 초범인 경우, 대처 방법‘존 스쿨’ 제도라고 들어보셨나요? 성매수 초범 남성에게 기소유예를 해주는 대신
+            재범방지교육을 받게 하는 제도로 1995년 미국에서 처음 도입되었습니다. 처벌이 아닌 교육을 통한 성매매 재범 방지 제도로 일종의 수강명령처분인데요. 성 매수
+            협의로 잡힌 남성들 중 많은 수가 본명 대신 ‘존(John)’이라는 이름을 댔기 때문이라고 합니다. 한국에서는 2005년 8월부터 시행되고 있습니다.이미지
+            출처 : 셔터스톡초범에 한해서, 진심으로 반성하는 태도를 보일 경우에만 위와 같이 대처할 수 있습니다. 조사시 변명보다는 다시는 재범하지 않을 것이라는 다짐을
+            적극적으로 표현하기 위해 반성문을 작성하여 제출하는 경우가 많습니다. 다만, 초범이라도 성매수를 한 대상이 미성년자라면 청소년성보호법’을 적용받아 처벌을
+            피하기 어렵습니다. 청소년성보호법에서는 성매매를 하도록 유인하거나 권유한 것만으로 처벌하는 규정이 있습니다.제13조(아동ㆍ청소년의 성을 사는 행위 등)①
+            아동ㆍ청소년의 성을 사는 행위를 한 자는 1년 이상 10년 이하의 징역 또는 2천만원 이상 5천만원 이하의 벌금에 처한다.② 아동ㆍ청소년의 성을 사기 위하여
+            아동ㆍ청소년을 유인하거나 성을 팔도록 권유한 자는 3년 이하의 징역 또는 3천만원 이하의 벌금에 처한다. [개정 2021. 3. 23.]③ 16세 미만의
+            아동ㆍ청소년 및 장애 아동ㆍ청소년을 대상으로 제1항 또는 제2항의 죄를 범한 경우에는 그 죄에 정한 형의 2분의 1까지 가중처벌한다. [신설 2020. 5.
+            19., 2020. 12. 8.]성매매를 입증하는 다양한 방법성매수자로 의심되는 것과 성매매를 했다고 입증하는 것은 별개입니다. 성매매 수사는 일반적으로
+            장부와 업소 실장 휴대전화의 통화기록, 메시지, 금전 거래 내역을 토대로 진행되는데, 업소 근처의 CCTV와 통화내역과 기지국 조회, 성판매 대상자의 진술을
+            복합적으로 고려하여 성구매 내용을 입증합니다. 때문에 현행범으로 단속되지 않았더라도 과거의 사실로 처벌될 수 있습니다.만약 성매매 초범으로 조사를 앞두고
+            있다면?초범이던, 자수를 했던 성매매는 엄연한 범죄입니다. 최근 들어 그 수법이 다양해지고 있는 만큼, 그에 맞는 대처방법이 필요합니다. 기소유예까지 연결된
+            다양한 사례는 아래 글을 통해 추가로 확인하실 수 있습니다.&amp;gt;&amp;gt; 사례 중심의 성매수 경찰조사 대처방법 확인하기로톡에서
+            한 주간 인기 있었던 상담사례와 성매매 초범에 대해 알아보았습니다. 만약, 성매매자수, 성매매단속, 성매매처벌 등으로 고민하고 있다면, 변호사와 상담하고
+            상황에 맞는 해결책을 빠르게 찾아보세요.</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>assistant</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>{ "toxicity": 0.0, "severe_toxicity": 0.0, "obscene": 0.0, "identity_attack": 0.0, "insult": 0.0, "threat": 0.0, "sexual_explicit": 0.0 }</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>929074f3-3a1d-4dbc-b51a-82778987af58</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>ready_for_export</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>{ "name": [ "_skip_labeling" ], "count": [ 2 ] }</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
         <is>
           <t>{ "name": [ "spam", "lang_mismatch", "pii", "not_appropriate", "hate_speech", "sexual_content", "quality", "toxicity", "humor", "creativity", "violence" ], "value": [ 0, 0, 0, 0, 0, 0, 0.5833333333333334, 0.08333333333333333, 0.08333333333333333, 0.4166666666666667, 0 ], "count": [ 3, 3, 3, 3, 3, 3, 3, 3, 3, 3, 3 ] }</t>
         </is>
